--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27997777-2DBF-40E9-AB79-F5CB2DEF213C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2E9085-AD0A-49AC-9AFF-BC30B1EF704E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
@@ -60,9 +60,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0"/>
-  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -728,14 +725,14 @@
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -88790,13 +88787,13 @@
       <c r="C4385" s="11">
         <v>6061553</v>
       </c>
-      <c r="D4385" s="14">
+      <c r="D4385" s="13">
         <v>-3.8</v>
       </c>
-      <c r="E4385" s="14">
+      <c r="E4385" s="13">
         <v>-6.3</v>
       </c>
-      <c r="F4385" s="14">
+      <c r="F4385" s="13">
         <v>-0.6</v>
       </c>
     </row>
@@ -88810,13 +88807,13 @@
       <c r="C4386" s="10">
         <v>6467002</v>
       </c>
-      <c r="D4386" s="14">
+      <c r="D4386" s="13">
         <v>-4.3</v>
       </c>
-      <c r="E4386" s="14">
+      <c r="E4386" s="13">
         <v>-7.9</v>
       </c>
-      <c r="F4386" s="14">
+      <c r="F4386" s="13">
         <v>-0.3</v>
       </c>
     </row>
@@ -88830,13 +88827,13 @@
       <c r="C4387" s="11">
         <v>5941863</v>
       </c>
-      <c r="D4387" s="14">
+      <c r="D4387" s="13">
         <v>-0.9</v>
       </c>
-      <c r="E4387" s="14">
+      <c r="E4387" s="13">
         <v>-5.9</v>
       </c>
-      <c r="F4387" s="14">
+      <c r="F4387" s="13">
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -88850,13 +88847,13 @@
       <c r="C4388" s="10">
         <v>5319928</v>
       </c>
-      <c r="D4388" s="14">
+      <c r="D4388" s="13">
         <v>3.4</v>
       </c>
-      <c r="E4388" s="14">
+      <c r="E4388" s="13">
         <v>-1.7</v>
       </c>
-      <c r="F4388" s="14">
+      <c r="F4388" s="13">
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -88870,13 +88867,13 @@
       <c r="C4389" s="11">
         <v>5679188</v>
       </c>
-      <c r="D4389" s="14">
+      <c r="D4389" s="13">
         <v>2.8</v>
       </c>
-      <c r="E4389" s="14">
+      <c r="E4389" s="13">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="F4389" s="14">
+      <c r="F4389" s="13">
         <v>6.4</v>
       </c>
     </row>
@@ -88890,13 +88887,13 @@
       <c r="C4390" s="10">
         <v>5791101</v>
       </c>
-      <c r="D4390" s="14">
+      <c r="D4390" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E4390" s="14">
+      <c r="E4390" s="13">
         <v>-2.1</v>
       </c>
-      <c r="F4390" s="14">
+      <c r="F4390" s="13">
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -88910,13 +88907,13 @@
       <c r="C4391" s="11">
         <v>5765987</v>
       </c>
-      <c r="D4391" s="14">
+      <c r="D4391" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E4391" s="14">
+      <c r="E4391" s="13">
         <v>-2.6</v>
       </c>
-      <c r="F4391" s="14">
+      <c r="F4391" s="13">
         <v>8.4</v>
       </c>
     </row>
@@ -88930,13 +88927,13 @@
       <c r="C4392" s="10">
         <v>6148550</v>
       </c>
-      <c r="D4392" s="14">
+      <c r="D4392" s="13">
         <v>-1.6</v>
       </c>
-      <c r="E4392" s="14">
+      <c r="E4392" s="13">
         <v>-4.7</v>
       </c>
-      <c r="F4392" s="14">
+      <c r="F4392" s="13">
         <v>2.9</v>
       </c>
     </row>
@@ -88950,13 +88947,13 @@
       <c r="C4393" s="11">
         <v>5821146</v>
       </c>
-      <c r="D4393" s="14">
+      <c r="D4393" s="13">
         <v>0.4</v>
       </c>
-      <c r="E4393" s="14">
+      <c r="E4393" s="13">
         <v>-5.9</v>
       </c>
-      <c r="F4393" s="14">
+      <c r="F4393" s="13">
         <v>7.7</v>
       </c>
     </row>
@@ -88970,13 +88967,13 @@
       <c r="C4394" s="10">
         <v>5236198</v>
       </c>
-      <c r="D4394" s="14">
+      <c r="D4394" s="13">
         <v>3.4</v>
       </c>
-      <c r="E4394" s="14">
+      <c r="E4394" s="13">
         <v>-2.4</v>
       </c>
-      <c r="F4394" s="14">
+      <c r="F4394" s="13">
         <v>11.9</v>
       </c>
     </row>
@@ -88990,13 +88987,13 @@
       <c r="C4395" s="11">
         <v>5638946</v>
       </c>
-      <c r="D4395" s="14">
+      <c r="D4395" s="13">
         <v>-2.4</v>
       </c>
-      <c r="E4395" s="14">
+      <c r="E4395" s="13">
         <v>-5.7</v>
       </c>
-      <c r="F4395" s="14">
+      <c r="F4395" s="13">
         <v>0.5</v>
       </c>
     </row>
@@ -89010,13 +89007,13 @@
       <c r="C4396" s="10">
         <v>6171121</v>
       </c>
-      <c r="D4396" s="14">
+      <c r="D4396" s="13">
         <v>-1.8</v>
       </c>
-      <c r="E4396" s="14">
+      <c r="E4396" s="13">
         <v>-8.8000000000000007</v>
       </c>
-      <c r="F4396" s="14">
+      <c r="F4396" s="13">
         <v>5.3</v>
       </c>
     </row>
@@ -89030,13 +89027,13 @@
       <c r="C4397" s="11">
         <v>5852190</v>
       </c>
-      <c r="D4397" s="14">
+      <c r="D4397" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E4397" s="14">
+      <c r="E4397" s="13">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="F4397" s="14">
+      <c r="F4397" s="13">
         <v>5.9</v>
       </c>
     </row>
@@ -89050,13 +89047,13 @@
       <c r="C4398" s="10">
         <v>5923777</v>
       </c>
-      <c r="D4398" s="14">
+      <c r="D4398" s="13">
         <v>0.4</v>
       </c>
-      <c r="E4398" s="14">
+      <c r="E4398" s="13">
         <v>-5.4</v>
       </c>
-      <c r="F4398" s="14">
+      <c r="F4398" s="13">
         <v>7.4</v>
       </c>
     </row>
@@ -89070,13 +89067,13 @@
       <c r="C4399" s="11">
         <v>5124740</v>
       </c>
-      <c r="D4399" s="14">
+      <c r="D4399" s="13">
         <v>7.8</v>
       </c>
-      <c r="E4399" s="14">
+      <c r="E4399" s="13">
         <v>-1</v>
       </c>
-      <c r="F4399" s="14">
+      <c r="F4399" s="13">
         <v>18</v>
       </c>
     </row>
@@ -89090,13 +89087,13 @@
       <c r="C4400" s="10">
         <v>4742092</v>
       </c>
-      <c r="D4400" s="14">
+      <c r="D4400" s="13">
         <v>6.6</v>
       </c>
-      <c r="E4400" s="14">
+      <c r="E4400" s="13">
         <v>-0.9</v>
       </c>
-      <c r="F4400" s="14">
+      <c r="F4400" s="13">
         <v>15.8</v>
       </c>
     </row>
@@ -89110,13 +89107,13 @@
       <c r="C4401" s="11">
         <v>4337895</v>
       </c>
-      <c r="D4401" s="14">
+      <c r="D4401" s="13">
         <v>5.5</v>
       </c>
-      <c r="E4401" s="14">
+      <c r="E4401" s="13">
         <v>0.6</v>
       </c>
-      <c r="F4401" s="14">
+      <c r="F4401" s="13">
         <v>12.6</v>
       </c>
     </row>
@@ -89130,13 +89127,13 @@
       <c r="C4402" s="10">
         <v>4256986</v>
       </c>
-      <c r="D4402" s="14">
+      <c r="D4402" s="13">
         <v>4.7</v>
       </c>
-      <c r="E4402" s="14">
+      <c r="E4402" s="13">
         <v>-2.7</v>
       </c>
-      <c r="F4402" s="14">
+      <c r="F4402" s="13">
         <v>13</v>
       </c>
     </row>
@@ -89150,13 +89147,13 @@
       <c r="C4403" s="11">
         <v>5295344</v>
       </c>
-      <c r="D4403" s="14">
+      <c r="D4403" s="13">
         <v>2.6</v>
       </c>
-      <c r="E4403" s="14">
+      <c r="E4403" s="13">
         <v>-2.9</v>
       </c>
-      <c r="F4403" s="14">
+      <c r="F4403" s="13">
         <v>6.1</v>
       </c>
     </row>
@@ -89170,13 +89167,13 @@
       <c r="C4404" s="10">
         <v>6007097</v>
       </c>
-      <c r="D4404" s="14">
+      <c r="D4404" s="13">
         <v>-1.8</v>
       </c>
-      <c r="E4404" s="14">
+      <c r="E4404" s="13">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="F4404" s="14">
+      <c r="F4404" s="13">
         <v>4.3</v>
       </c>
     </row>
@@ -89190,13 +89187,13 @@
       <c r="C4405" s="11">
         <v>6589787</v>
       </c>
-      <c r="D4405" s="14">
+      <c r="D4405" s="13">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="E4405" s="14">
+      <c r="E4405" s="13">
         <v>-7.3</v>
       </c>
-      <c r="F4405" s="14">
+      <c r="F4405" s="13">
         <v>-0.8</v>
       </c>
     </row>
@@ -89210,13 +89207,13 @@
       <c r="C4406" s="10">
         <v>6927724</v>
       </c>
-      <c r="D4406" s="14">
+      <c r="D4406" s="13">
         <v>-5.0999999999999996</v>
       </c>
-      <c r="E4406" s="14">
+      <c r="E4406" s="13">
         <v>-8.5</v>
       </c>
-      <c r="F4406" s="14">
+      <c r="F4406" s="13">
         <v>-1.1000000000000001</v>
       </c>
     </row>
@@ -89230,13 +89227,13 @@
       <c r="C4407" s="11">
         <v>6447778</v>
       </c>
-      <c r="D4407" s="14">
+      <c r="D4407" s="13">
         <v>-1.6</v>
       </c>
-      <c r="E4407" s="14">
+      <c r="E4407" s="13">
         <v>-6.4</v>
       </c>
-      <c r="F4407" s="14">
+      <c r="F4407" s="13">
         <v>3.7</v>
       </c>
     </row>
@@ -89250,13 +89247,13 @@
       <c r="C4408" s="10">
         <v>5946847</v>
       </c>
-      <c r="D4408" s="14">
+      <c r="D4408" s="13">
         <v>-1.2</v>
       </c>
-      <c r="E4408" s="14">
+      <c r="E4408" s="13">
         <v>-4.3</v>
       </c>
-      <c r="F4408" s="14">
+      <c r="F4408" s="13">
         <v>2.6</v>
       </c>
     </row>
@@ -89270,13 +89267,13 @@
       <c r="C4409" s="11">
         <v>5719679</v>
       </c>
-      <c r="D4409" s="14">
+      <c r="D4409" s="13">
         <v>-1.3</v>
       </c>
-      <c r="E4409" s="14">
+      <c r="E4409" s="13">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="F4409" s="14">
+      <c r="F4409" s="13">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -89290,13 +89287,13 @@
       <c r="C4410" s="10">
         <v>6398362</v>
       </c>
-      <c r="D4410" s="14">
+      <c r="D4410" s="13">
         <v>-1.3</v>
       </c>
-      <c r="E4410" s="14">
+      <c r="E4410" s="13">
         <v>-8.1</v>
       </c>
-      <c r="F4410" s="14">
+      <c r="F4410" s="13">
         <v>4</v>
       </c>
     </row>
@@ -89310,13 +89307,13 @@
       <c r="C4411" s="11">
         <v>6152088</v>
       </c>
-      <c r="D4411" s="14">
+      <c r="D4411" s="13">
         <v>0.8</v>
       </c>
-      <c r="E4411" s="14">
+      <c r="E4411" s="13">
         <v>-1.8</v>
       </c>
-      <c r="F4411" s="14">
+      <c r="F4411" s="13">
         <v>4.8</v>
       </c>
     </row>
@@ -89330,13 +89327,13 @@
       <c r="C4412" s="10">
         <v>6331629</v>
       </c>
-      <c r="D4412" s="14">
+      <c r="D4412" s="13">
         <v>-1.2</v>
       </c>
-      <c r="E4412" s="14">
+      <c r="E4412" s="13">
         <v>-4.7</v>
       </c>
-      <c r="F4412" s="14">
+      <c r="F4412" s="13">
         <v>3.3</v>
       </c>
     </row>
@@ -89350,13 +89347,13 @@
       <c r="C4413" s="11">
         <v>6319587</v>
       </c>
-      <c r="D4413" s="14">
+      <c r="D4413" s="13">
         <v>-0.4</v>
       </c>
-      <c r="E4413" s="14">
+      <c r="E4413" s="13">
         <v>-3.6</v>
       </c>
-      <c r="F4413" s="14">
+      <c r="F4413" s="13">
         <v>4.3</v>
       </c>
     </row>
@@ -89370,13 +89367,13 @@
       <c r="C4414" s="10">
         <v>6523224</v>
       </c>
-      <c r="D4414" s="14">
+      <c r="D4414" s="13">
         <v>-2.1</v>
       </c>
-      <c r="E4414" s="14">
+      <c r="E4414" s="13">
         <v>-5.6</v>
       </c>
-      <c r="F4414" s="14">
+      <c r="F4414" s="13">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -89390,13 +89387,13 @@
       <c r="C4415" s="11">
         <v>5806316</v>
       </c>
-      <c r="D4415" s="14">
+      <c r="D4415" s="13">
         <v>-0.6</v>
       </c>
-      <c r="E4415" s="14">
+      <c r="E4415" s="13">
         <v>-7</v>
       </c>
-      <c r="F4415" s="14">
+      <c r="F4415" s="13">
         <v>5.4</v>
       </c>
     </row>
@@ -89404,10 +89401,10 @@
       <c r="A4416" s="7">
         <v>46054</v>
       </c>
-      <c r="B4416" s="13">
+      <c r="B4416" s="12">
         <v>231460034</v>
       </c>
-      <c r="C4416" s="13">
+      <c r="C4416" s="12">
         <v>5410295</v>
       </c>
       <c r="D4416" s="14">
@@ -89424,10 +89421,10 @@
       <c r="A4417" s="7">
         <v>46055</v>
       </c>
-      <c r="B4417" s="13">
+      <c r="B4417" s="12">
         <v>263280887</v>
       </c>
-      <c r="C4417" s="13">
+      <c r="C4417" s="12">
         <v>6158909</v>
       </c>
       <c r="D4417" s="14">
@@ -89444,10 +89441,10 @@
       <c r="A4418" s="7">
         <v>46056</v>
       </c>
-      <c r="B4418" s="13">
+      <c r="B4418" s="12">
         <v>253722193</v>
       </c>
-      <c r="C4418" s="13">
+      <c r="C4418" s="12">
         <v>5941039</v>
       </c>
       <c r="D4418" s="14">
@@ -89464,10 +89461,10 @@
       <c r="A4419" s="7">
         <v>46057</v>
       </c>
-      <c r="B4419" s="13">
+      <c r="B4419" s="12">
         <v>236014580</v>
       </c>
-      <c r="C4419" s="13">
+      <c r="C4419" s="12">
         <v>5541039</v>
       </c>
       <c r="D4419" s="14">
@@ -89484,10 +89481,10 @@
       <c r="A4420" s="7">
         <v>46058</v>
       </c>
-      <c r="B4420" s="13">
+      <c r="B4420" s="12">
         <v>218842000</v>
       </c>
-      <c r="C4420" s="13">
+      <c r="C4420" s="12">
         <v>5145541</v>
       </c>
       <c r="D4420" s="14">
@@ -89504,10 +89501,10 @@
       <c r="A4421" s="7">
         <v>46059</v>
       </c>
-      <c r="B4421" s="13">
+      <c r="B4421" s="12">
         <v>225019493</v>
       </c>
-      <c r="C4421" s="13">
+      <c r="C4421" s="12">
         <v>5289603</v>
       </c>
       <c r="D4421" s="14">
@@ -89524,10 +89521,10 @@
       <c r="A4422" s="7">
         <v>46060</v>
       </c>
-      <c r="B4422" s="13">
+      <c r="B4422" s="12">
         <v>239694610</v>
       </c>
-      <c r="C4422" s="13">
+      <c r="C4422" s="12">
         <v>5621023</v>
       </c>
       <c r="D4422" s="14">
@@ -89544,10 +89541,10 @@
       <c r="A4423" s="7">
         <v>46061</v>
       </c>
-      <c r="B4423" s="13">
+      <c r="B4423" s="12">
         <v>260957149</v>
       </c>
-      <c r="C4423" s="13">
+      <c r="C4423" s="12">
         <v>6107516</v>
       </c>
       <c r="D4423" s="14">
@@ -89564,10 +89561,10 @@
       <c r="A4424" s="7">
         <v>46062</v>
       </c>
-      <c r="B4424" s="13">
+      <c r="B4424" s="12">
         <v>257402574</v>
       </c>
-      <c r="C4424" s="13">
+      <c r="C4424" s="12">
         <v>6037724</v>
       </c>
       <c r="D4424" s="14">
@@ -89584,10 +89581,10 @@
       <c r="A4425" s="7">
         <v>46063</v>
       </c>
-      <c r="B4425" s="13">
+      <c r="B4425" s="12">
         <v>251628937</v>
       </c>
-      <c r="C4425" s="13">
+      <c r="C4425" s="12">
         <v>5896186</v>
       </c>
       <c r="D4425" s="14">
@@ -89604,10 +89601,10 @@
       <c r="A4426" s="7">
         <v>46064</v>
       </c>
-      <c r="B4426" s="13">
+      <c r="B4426" s="12">
         <v>233079151</v>
       </c>
-      <c r="C4426" s="13">
+      <c r="C4426" s="12">
         <v>5440980</v>
       </c>
       <c r="D4426" s="14">
@@ -89624,10 +89621,10 @@
       <c r="A4427" s="7">
         <v>46065</v>
       </c>
-      <c r="B4427" s="13">
+      <c r="B4427" s="12">
         <v>224767484</v>
       </c>
-      <c r="C4427" s="13">
+      <c r="C4427" s="12">
         <v>5255214</v>
       </c>
       <c r="D4427" s="14">
@@ -89644,10 +89641,10 @@
       <c r="A4428" s="7">
         <v>46066</v>
       </c>
-      <c r="B4428" s="13">
+      <c r="B4428" s="12">
         <v>212685300</v>
       </c>
-      <c r="C4428" s="13">
+      <c r="C4428" s="12">
         <v>4995680</v>
       </c>
       <c r="D4428" s="14">
@@ -89664,10 +89661,10 @@
       <c r="A4429" s="7">
         <v>46067</v>
       </c>
-      <c r="B4429" s="13">
+      <c r="B4429" s="12">
         <v>188537193</v>
       </c>
-      <c r="C4429" s="13">
+      <c r="C4429" s="12">
         <v>4430044</v>
       </c>
       <c r="D4429" s="14">
@@ -89684,10 +89681,10 @@
       <c r="A4430" s="7">
         <v>46068</v>
       </c>
-      <c r="B4430" s="13">
+      <c r="B4430" s="12">
         <v>165558989</v>
       </c>
-      <c r="C4430" s="13">
+      <c r="C4430" s="12">
         <v>3883804</v>
       </c>
       <c r="D4430" s="14">
@@ -89704,10 +89701,10 @@
       <c r="A4431" s="2">
         <v>46069</v>
       </c>
-      <c r="B4431" s="13">
+      <c r="B4431" s="12">
         <v>174403457</v>
       </c>
-      <c r="C4431" s="13">
+      <c r="C4431" s="12">
         <v>4088389</v>
       </c>
       <c r="D4431" s="14">
@@ -89724,10 +89721,10 @@
       <c r="A4432" s="2">
         <v>46070</v>
       </c>
-      <c r="B4432" s="13">
+      <c r="B4432" s="12">
         <v>164180373</v>
       </c>
-      <c r="C4432" s="13">
+      <c r="C4432" s="12">
         <v>3844412</v>
       </c>
       <c r="D4432" s="14">
@@ -89744,10 +89741,10 @@
       <c r="A4433" s="2">
         <v>46071</v>
       </c>
-      <c r="B4433" s="13">
+      <c r="B4433" s="12">
         <v>169013046</v>
       </c>
-      <c r="C4433" s="13">
+      <c r="C4433" s="12">
         <v>3964379</v>
       </c>
       <c r="D4433" s="14">
@@ -89764,10 +89761,10 @@
       <c r="A4434" s="2">
         <v>46072</v>
       </c>
-      <c r="B4434" s="13">
+      <c r="B4434" s="12">
         <v>187310799</v>
       </c>
-      <c r="C4434" s="13">
+      <c r="C4434" s="12">
         <v>4398818</v>
       </c>
       <c r="D4434" s="14">
@@ -89784,10 +89781,10 @@
       <c r="A4435" s="2">
         <v>46073</v>
       </c>
-      <c r="B4435" s="13">
+      <c r="B4435" s="12">
         <v>180700961</v>
       </c>
-      <c r="C4435" s="13">
+      <c r="C4435" s="12">
         <v>4239089</v>
       </c>
       <c r="D4435" s="14">
@@ -89804,10 +89801,10 @@
       <c r="A4436" s="2">
         <v>46074</v>
       </c>
-      <c r="B4436" s="13">
+      <c r="B4436" s="12">
         <v>154463409</v>
       </c>
-      <c r="C4436" s="13">
+      <c r="C4436" s="12">
         <v>3619697</v>
       </c>
       <c r="D4436" s="14">
@@ -89824,10 +89821,10 @@
       <c r="A4437" s="2">
         <v>46075</v>
       </c>
-      <c r="B4437" s="13">
+      <c r="B4437" s="12">
         <v>132590218</v>
       </c>
-      <c r="C4437" s="13">
+      <c r="C4437" s="12">
         <v>3097651</v>
       </c>
       <c r="D4437" s="14">
@@ -89844,10 +89841,10 @@
       <c r="A4438" s="2">
         <v>46076</v>
       </c>
-      <c r="B4438" s="13">
+      <c r="B4438" s="12">
         <v>171280960</v>
       </c>
-      <c r="C4438" s="13">
+      <c r="C4438" s="12">
         <v>4003942</v>
       </c>
       <c r="D4438" s="14">
@@ -89864,10 +89861,10 @@
       <c r="A4439" s="2">
         <v>46077</v>
       </c>
-      <c r="B4439" s="13">
+      <c r="B4439" s="12">
         <v>204191951</v>
       </c>
-      <c r="C4439" s="13">
+      <c r="C4439" s="12">
         <v>4770693</v>
       </c>
       <c r="D4439" s="14">
@@ -89884,10 +89881,10 @@
       <c r="A4440" s="2">
         <v>46078</v>
       </c>
-      <c r="B4440" s="13">
+      <c r="B4440" s="12">
         <v>191058803</v>
       </c>
-      <c r="C4440" s="13">
+      <c r="C4440" s="12">
         <v>4464182</v>
       </c>
       <c r="D4440" s="14">
@@ -89900,178 +89897,364 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4441" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4441" s="2">
         <v>46079</v>
       </c>
-      <c r="E4441" s="12">
-        <v>4</v>
-      </c>
-      <c r="F4441" s="12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4442" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4441" s="12">
+        <v>183959183</v>
+      </c>
+      <c r="C4441" s="12">
+        <v>4297014</v>
+      </c>
+      <c r="D4441" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E4441" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="F4441" s="14">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4442" s="2">
         <v>46080</v>
       </c>
-      <c r="E4442" s="1">
-        <v>6</v>
-      </c>
-      <c r="F4442" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4443" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4442" s="12">
+        <v>180826017</v>
+      </c>
+      <c r="C4442" s="12">
+        <v>4212989</v>
+      </c>
+      <c r="D4442" s="14">
+        <v>7.7</v>
+      </c>
+      <c r="E4442" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="F4442" s="14">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4443" s="2">
         <v>46081</v>
       </c>
-      <c r="E4443" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4443" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4444" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4443" s="12">
+        <v>164812950</v>
+      </c>
+      <c r="C4443" s="12">
+        <v>3830825</v>
+      </c>
+      <c r="D4443" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E4443" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="F4443" s="14">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4444" s="2">
         <v>46082</v>
       </c>
-      <c r="E4444" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4444" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4445" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4444" s="12">
+        <v>155680397</v>
+      </c>
+      <c r="C4444" s="12">
+        <v>3620962</v>
+      </c>
+      <c r="D4444" s="13">
+        <v>8.1</v>
+      </c>
+      <c r="E4444" s="13">
+        <v>6.7</v>
+      </c>
+      <c r="F4444" s="13">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4445" s="2">
         <v>46083</v>
       </c>
-      <c r="E4445" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4445" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4446" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4445" s="12">
+        <v>179407453</v>
+      </c>
+      <c r="C4445" s="12">
+        <v>4176814</v>
+      </c>
+      <c r="D4445" s="13">
+        <v>6.7</v>
+      </c>
+      <c r="E4445" s="13">
+        <v>4.2</v>
+      </c>
+      <c r="F4445" s="13">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4446" s="2">
         <v>46084</v>
       </c>
-      <c r="E4446" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4446" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4447" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4446" s="12">
+        <v>185583168</v>
+      </c>
+      <c r="C4446" s="12">
+        <v>4323057</v>
+      </c>
+      <c r="D4446" s="13">
+        <v>7.4</v>
+      </c>
+      <c r="E4446" s="13">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F4446" s="13">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4447" s="2">
         <v>46085</v>
       </c>
-      <c r="E4447" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4447" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4448" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4447" s="12">
+        <v>172414802</v>
+      </c>
+      <c r="C4447" s="12">
+        <v>4010199</v>
+      </c>
+      <c r="D4447" s="13">
+        <v>7.9</v>
+      </c>
+      <c r="E4447" s="13">
+        <v>2</v>
+      </c>
+      <c r="F4447" s="13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4448" s="2">
         <v>46086</v>
       </c>
-      <c r="E4448" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4448" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4449" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4448" s="12">
+        <v>171944727</v>
+      </c>
+      <c r="C4448" s="12">
+        <v>3993682</v>
+      </c>
+      <c r="D4448" s="13">
+        <v>8</v>
+      </c>
+      <c r="E4448" s="13">
+        <v>1</v>
+      </c>
+      <c r="F4448" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4449" s="2">
         <v>46087</v>
       </c>
-      <c r="E4449" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4449" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4450" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4449" s="12">
+        <v>178862382</v>
+      </c>
+      <c r="C4449" s="12">
+        <v>4174418</v>
+      </c>
+      <c r="D4449" s="13">
+        <v>6</v>
+      </c>
+      <c r="E4449" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="F4449" s="13">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4450" s="2">
         <v>46088</v>
       </c>
-      <c r="E4450" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4450" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4451" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4450" s="12">
+        <v>177304965</v>
+      </c>
+      <c r="C4450" s="12">
+        <v>4135158</v>
+      </c>
+      <c r="D4450" s="13">
+        <v>3.7</v>
+      </c>
+      <c r="E4450" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="F4450" s="13">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4451" s="2">
         <v>46089</v>
       </c>
-      <c r="E4451" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4451" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4452" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4451" s="12">
+        <v>168972728</v>
+      </c>
+      <c r="C4451" s="12">
+        <v>3942007</v>
+      </c>
+      <c r="D4451" s="13">
+        <v>4.7</v>
+      </c>
+      <c r="E4451" s="13">
+        <v>-3.8</v>
+      </c>
+      <c r="F4451" s="13">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4452" s="2">
         <v>46090</v>
       </c>
-      <c r="E4452" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4452" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4453" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4452" s="12">
+        <v>194284135</v>
+      </c>
+      <c r="C4452" s="12">
+        <v>4551875</v>
+      </c>
+      <c r="D4452" s="13">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E4452" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="F4452" s="13">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4453" s="2">
         <v>46091</v>
       </c>
-      <c r="E4453" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4453" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4454" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4453" s="12">
+        <v>188047454</v>
+      </c>
+      <c r="C4453" s="12">
+        <v>4422645</v>
+      </c>
+      <c r="D4453" s="13">
+        <v>5</v>
+      </c>
+      <c r="E4453" s="13">
+        <v>-2.1</v>
+      </c>
+      <c r="F4453" s="13">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4454" s="2">
         <v>46092</v>
       </c>
-      <c r="E4454" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4454" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4455" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4454" s="12">
+        <v>180260471</v>
+      </c>
+      <c r="C4454" s="12">
+        <v>4237626</v>
+      </c>
+      <c r="D4454" s="13">
+        <v>6.7</v>
+      </c>
+      <c r="E4454" s="13">
+        <v>-0.6</v>
+      </c>
+      <c r="F4454" s="13">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4455" s="2">
         <v>46093</v>
       </c>
-    </row>
-    <row r="4456" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4455" s="12">
+        <v>182046592</v>
+      </c>
+      <c r="C4455" s="12">
+        <v>4270524</v>
+      </c>
+      <c r="D4455" s="13">
+        <v>6.9</v>
+      </c>
+      <c r="E4455" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="F4455" s="13">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4456" s="2">
         <v>46094</v>
       </c>
-    </row>
-    <row r="4457" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4456" s="12">
+        <v>184703467</v>
+      </c>
+      <c r="C4456" s="12">
+        <v>4344503</v>
+      </c>
+      <c r="D4456" s="13">
+        <v>5.6</v>
+      </c>
+      <c r="E4456" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="F4456" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4457" s="2">
         <v>46095</v>
       </c>
-    </row>
-    <row r="4458" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4457" s="12">
+        <v>160400696</v>
+      </c>
+      <c r="C4457" s="12">
+        <v>3774073</v>
+      </c>
+      <c r="D4457" s="13">
+        <v>6.7</v>
+      </c>
+      <c r="E4457" s="13">
+        <v>-1.7</v>
+      </c>
+      <c r="F4457" s="13">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4458" s="2">
         <v>46096</v>
+      </c>
+      <c r="B4458" s="12">
+        <v>152227505</v>
+      </c>
+      <c r="C4458" s="12">
+        <v>3583871</v>
+      </c>
+      <c r="D4458" s="13">
+        <v>7.8</v>
+      </c>
+      <c r="E4458" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F4458" s="13">
+        <v>11.1</v>
       </c>
     </row>
     <row r="4459" spans="1:6" x14ac:dyDescent="0.3">

--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2E9085-AD0A-49AC-9AFF-BC30B1EF704E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F6BBC1-C2B9-4167-B43F-6A72F126C104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
@@ -688,7 +688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,6 +733,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -90261,108 +90264,207 @@
       <c r="A4459" s="2">
         <v>46097</v>
       </c>
+      <c r="E4459" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4459" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="4460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4460" s="2">
         <v>46098</v>
       </c>
+      <c r="E4460" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4460" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="4461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4461" s="2">
         <v>46099</v>
       </c>
+      <c r="E4461" s="1">
+        <v>7</v>
+      </c>
+      <c r="F4461" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="4462" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4462" s="2">
         <v>46100</v>
       </c>
+      <c r="E4462" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4462" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="4463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4463" s="2">
         <v>46101</v>
       </c>
+      <c r="E4463" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4463" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="4464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4464" s="2">
         <v>46102</v>
       </c>
-    </row>
-    <row r="4465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4464" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4464" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4465" s="2">
         <v>46103</v>
       </c>
-    </row>
-    <row r="4466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4465" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4465" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4466" s="2">
         <v>46104</v>
       </c>
-    </row>
-    <row r="4467" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4466" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4466" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4467" s="2">
         <v>46105</v>
       </c>
-    </row>
-    <row r="4468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4467" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4467" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4468" s="2">
         <v>46106</v>
       </c>
-    </row>
-    <row r="4469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4468" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4468" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4469" s="2">
         <v>46107</v>
       </c>
-    </row>
-    <row r="4470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4469" s="1">
+        <v>7</v>
+      </c>
+      <c r="F4469" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4470" s="2">
         <v>46108</v>
       </c>
-    </row>
-    <row r="4471" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4470" s="1">
+        <v>7</v>
+      </c>
+      <c r="F4470" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4471" s="2">
         <v>46109</v>
       </c>
-    </row>
-    <row r="4472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4471" s="1">
+        <v>7</v>
+      </c>
+      <c r="F4471" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4472" s="2">
         <v>46110</v>
       </c>
-    </row>
-    <row r="4473" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4472" s="1">
+        <v>8</v>
+      </c>
+      <c r="F4472" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4473" s="2">
         <v>46111</v>
       </c>
-    </row>
-    <row r="4474" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4474" s="2">
+      <c r="E4473" s="1">
+        <v>8</v>
+      </c>
+      <c r="F4473" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4474" s="3">
         <v>46112</v>
       </c>
-    </row>
-    <row r="4475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4474" s="15"/>
+      <c r="C4474" s="15"/>
+      <c r="D4474" s="4"/>
+      <c r="E4474" s="4">
+        <v>8</v>
+      </c>
+      <c r="F4474" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4475" s="2">
         <v>46113</v>
       </c>
     </row>
-    <row r="4476" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4476" s="2">
         <v>46114</v>
       </c>
     </row>
-    <row r="4477" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4477" s="2">
         <v>46115</v>
       </c>
     </row>
-    <row r="4478" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4478" s="2">
         <v>46116</v>
       </c>
     </row>
-    <row r="4479" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4479" s="2">
         <v>46117</v>
       </c>
     </row>
-    <row r="4480" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4480" s="2">
         <v>46118</v>
       </c>

--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F6BBC1-C2B9-4167-B43F-6A72F126C104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1555C2E-7A5A-4473-93C8-6CCB58B57719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
@@ -734,8 +734,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -90260,291 +90260,657 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="4459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4459" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4459" s="2">
         <v>46097</v>
       </c>
-      <c r="E4459" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4459" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4460" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4459" s="12">
+        <v>152227505</v>
+      </c>
+      <c r="C4459" s="12">
+        <v>3583871</v>
+      </c>
+      <c r="D4459" s="15">
+        <v>7.8</v>
+      </c>
+      <c r="E4459" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F4459" s="15">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4460" s="2">
         <v>46098</v>
       </c>
-      <c r="E4460" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4460" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4461" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4460" s="12">
+        <v>161279488</v>
+      </c>
+      <c r="C4460" s="12">
+        <v>3799006</v>
+      </c>
+      <c r="D4460" s="15">
+        <v>9</v>
+      </c>
+      <c r="E4460" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="F4460" s="15">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4461" s="2">
         <v>46099</v>
       </c>
-      <c r="E4461" s="1">
-        <v>7</v>
-      </c>
-      <c r="F4461" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4462" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4461" s="12">
+        <v>149887477</v>
+      </c>
+      <c r="C4461" s="12">
+        <v>3526083</v>
+      </c>
+      <c r="D4461" s="15">
+        <v>10.8</v>
+      </c>
+      <c r="E4461" s="15">
+        <v>3.3</v>
+      </c>
+      <c r="F4461" s="15">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4462" s="2">
         <v>46100</v>
       </c>
-      <c r="E4462" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4462" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4463" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4462" s="12">
+        <v>161055628</v>
+      </c>
+      <c r="C4462" s="12">
+        <v>3796787</v>
+      </c>
+      <c r="D4462" s="15">
+        <v>8.6</v>
+      </c>
+      <c r="E4462" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="F4462" s="15">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4463" s="2">
         <v>46101</v>
       </c>
-      <c r="E4463" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4463" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4464" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4463" s="12">
+        <v>154958138</v>
+      </c>
+      <c r="C4463" s="12">
+        <v>3646994</v>
+      </c>
+      <c r="D4463" s="15">
+        <v>9.6</v>
+      </c>
+      <c r="E4463" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F4463" s="15">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4464" s="2">
         <v>46102</v>
       </c>
-      <c r="E4464" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4464" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4465" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4464" s="12">
+        <v>149312872</v>
+      </c>
+      <c r="C4464" s="12">
+        <v>3514151</v>
+      </c>
+      <c r="D4464" s="15">
+        <v>10.1</v>
+      </c>
+      <c r="E4464" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F4464" s="15">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4465" s="2">
         <v>46103</v>
       </c>
-      <c r="E4465" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4465" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4466" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4465" s="12">
+        <v>127022204</v>
+      </c>
+      <c r="C4465" s="12">
+        <v>2981501</v>
+      </c>
+      <c r="D4465" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E4465" s="15">
+        <v>2</v>
+      </c>
+      <c r="F4465" s="15">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4466" s="2">
         <v>46104</v>
       </c>
-      <c r="E4466" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4466" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4467" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4466" s="12">
+        <v>115810115</v>
+      </c>
+      <c r="C4466" s="12">
+        <v>2712255</v>
+      </c>
+      <c r="D4466" s="15">
+        <v>11.2</v>
+      </c>
+      <c r="E4466" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="F4466" s="15">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4467" s="2">
         <v>46105</v>
       </c>
-      <c r="E4467" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4467" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4468" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4467" s="12">
+        <v>131331642</v>
+      </c>
+      <c r="C4467" s="12">
+        <v>3067061</v>
+      </c>
+      <c r="D4467" s="15">
+        <v>11.1</v>
+      </c>
+      <c r="E4467" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="F4467" s="15">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4468" s="2">
         <v>46106</v>
       </c>
-      <c r="E4468" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4468" s="1">
+      <c r="B4468" s="12">
+        <v>131675317</v>
+      </c>
+      <c r="C4468" s="12">
+        <v>3072834</v>
+      </c>
+      <c r="D4468" s="15">
+        <v>11.4</v>
+      </c>
+      <c r="E4468" s="15">
+        <v>3.9</v>
+      </c>
+      <c r="F4468" s="15">
         <v>19</v>
       </c>
     </row>
-    <row r="4469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4469" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4469" s="2">
         <v>46107</v>
       </c>
-      <c r="E4469" s="1">
-        <v>7</v>
-      </c>
-      <c r="F4469" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4470" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4469" s="12">
+        <v>126808040</v>
+      </c>
+      <c r="C4469" s="12">
+        <v>2961328</v>
+      </c>
+      <c r="D4469" s="15">
+        <v>12.6</v>
+      </c>
+      <c r="E4469" s="15">
+        <v>9.5</v>
+      </c>
+      <c r="F4469" s="15">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4470" s="2">
         <v>46108</v>
       </c>
-      <c r="E4470" s="1">
-        <v>7</v>
-      </c>
-      <c r="F4470" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4471" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4470" s="12">
+        <v>119607143</v>
+      </c>
+      <c r="C4470" s="12">
+        <v>2794135</v>
+      </c>
+      <c r="D4470" s="15">
+        <v>14</v>
+      </c>
+      <c r="E4470" s="15">
+        <v>5</v>
+      </c>
+      <c r="F4470" s="15">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4471" s="2">
         <v>46109</v>
       </c>
-      <c r="E4471" s="1">
-        <v>7</v>
-      </c>
-      <c r="F4471" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4472" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4471" s="12">
+        <v>110740660</v>
+      </c>
+      <c r="C4471" s="12">
+        <v>2587341</v>
+      </c>
+      <c r="D4471" s="15">
+        <v>16</v>
+      </c>
+      <c r="E4471" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="F4471" s="15">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4472" s="2">
         <v>46110</v>
       </c>
-      <c r="E4472" s="1">
-        <v>8</v>
-      </c>
-      <c r="F4472" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4473" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4472" s="12">
+        <v>92493702</v>
+      </c>
+      <c r="C4472" s="12">
+        <v>2162203</v>
+      </c>
+      <c r="D4472" s="15">
+        <v>15.5</v>
+      </c>
+      <c r="E4472" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="F4472" s="15">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4473" s="2">
         <v>46111</v>
       </c>
-      <c r="E4473" s="1">
-        <v>8</v>
-      </c>
-      <c r="F4473" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4474" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4473" s="12">
+        <v>84512783</v>
+      </c>
+      <c r="C4473" s="12">
+        <v>1975528</v>
+      </c>
+      <c r="D4473" s="15">
+        <v>14.5</v>
+      </c>
+      <c r="E4473" s="15">
+        <v>7.2</v>
+      </c>
+      <c r="F4473" s="15">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4474" s="3">
         <v>46112</v>
       </c>
-      <c r="B4474" s="15"/>
-      <c r="C4474" s="15"/>
-      <c r="D4474" s="4"/>
-      <c r="E4474" s="4">
-        <v>8</v>
-      </c>
-      <c r="F4474" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4475" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4474" s="12">
+        <v>108455150</v>
+      </c>
+      <c r="C4474" s="12">
+        <v>2534255</v>
+      </c>
+      <c r="D4474" s="15">
+        <v>13</v>
+      </c>
+      <c r="E4474" s="15">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F4474" s="15">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4475" s="2">
         <v>46113</v>
       </c>
-    </row>
-    <row r="4476" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4475" s="12">
+        <v>116253815</v>
+      </c>
+      <c r="C4475" s="12">
+        <v>2722597</v>
+      </c>
+      <c r="D4475" s="15">
+        <v>12.9</v>
+      </c>
+      <c r="E4475" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="F4475" s="15">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4476" s="2">
         <v>46114</v>
       </c>
-    </row>
-    <row r="4477" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4476" s="12">
+        <v>113163968</v>
+      </c>
+      <c r="C4476" s="12">
+        <v>2657097</v>
+      </c>
+      <c r="D4476" s="15">
+        <v>13.1</v>
+      </c>
+      <c r="E4476" s="15">
+        <v>10.1</v>
+      </c>
+      <c r="F4476" s="15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4477" s="2">
         <v>46115</v>
       </c>
-    </row>
-    <row r="4478" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4477" s="12">
+        <v>110028996</v>
+      </c>
+      <c r="C4477" s="12">
+        <v>2589721</v>
+      </c>
+      <c r="D4477" s="15">
+        <v>14.4</v>
+      </c>
+      <c r="E4477" s="15">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F4477" s="15">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4478" s="2">
         <v>46116</v>
       </c>
-    </row>
-    <row r="4479" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4478" s="12">
+        <v>103998595</v>
+      </c>
+      <c r="C4478" s="12">
+        <v>2447428</v>
+      </c>
+      <c r="D4478" s="15">
+        <v>15</v>
+      </c>
+      <c r="E4478" s="15">
+        <v>6.7</v>
+      </c>
+      <c r="F4478" s="15">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4479" s="2">
         <v>46117</v>
       </c>
-    </row>
-    <row r="4480" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4479" s="12">
+        <v>93885823</v>
+      </c>
+      <c r="C4479" s="12">
+        <v>2208762</v>
+      </c>
+      <c r="D4479" s="15">
+        <v>14</v>
+      </c>
+      <c r="E4479" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="F4479" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4480" s="2">
         <v>46118</v>
       </c>
-    </row>
-    <row r="4481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4480" s="12">
+        <v>84016293</v>
+      </c>
+      <c r="C4480" s="12">
+        <v>1982207</v>
+      </c>
+      <c r="D4480" s="15">
+        <v>14.2</v>
+      </c>
+      <c r="E4480" s="15">
+        <v>8.4</v>
+      </c>
+      <c r="F4480" s="15">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4481" s="2">
         <v>46119</v>
       </c>
-    </row>
-    <row r="4482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4481" s="12">
+        <v>114348356</v>
+      </c>
+      <c r="C4481" s="12">
+        <v>2687323</v>
+      </c>
+      <c r="D4481" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="E4481" s="15">
+        <v>9.5</v>
+      </c>
+      <c r="F4481" s="15">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4482" s="2">
         <v>46120</v>
       </c>
-    </row>
-    <row r="4483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4482" s="12">
+        <v>124845506</v>
+      </c>
+      <c r="C4482" s="12">
+        <v>2926523</v>
+      </c>
+      <c r="D4482" s="15">
+        <v>10.4</v>
+      </c>
+      <c r="E4482" s="15">
+        <v>6.2</v>
+      </c>
+      <c r="F4482" s="15">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4483" s="2">
         <v>46121</v>
       </c>
-    </row>
-    <row r="4484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4483" s="12">
+        <v>120297821</v>
+      </c>
+      <c r="C4483" s="12">
+        <v>2821860</v>
+      </c>
+      <c r="D4483" s="15">
+        <v>12</v>
+      </c>
+      <c r="E4483" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="F4483" s="15">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4484" s="2">
         <v>46122</v>
       </c>
-    </row>
-    <row r="4485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4484" s="12">
+        <v>123067538</v>
+      </c>
+      <c r="C4484" s="12">
+        <v>2885559</v>
+      </c>
+      <c r="D4484" s="15">
+        <v>12.6</v>
+      </c>
+      <c r="E4484" s="15">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F4484" s="15">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4485" s="2">
         <v>46123</v>
       </c>
-    </row>
-    <row r="4486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4485" s="12">
+        <v>105864719</v>
+      </c>
+      <c r="C4485" s="12">
+        <v>2479759</v>
+      </c>
+      <c r="D4485" s="15">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4485" s="15">
+        <v>12.6</v>
+      </c>
+      <c r="F4485" s="15">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4486" s="2">
         <v>46124</v>
       </c>
-    </row>
-    <row r="4487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4486" s="12">
+        <v>87897087</v>
+      </c>
+      <c r="C4486" s="12">
+        <v>2058917</v>
+      </c>
+      <c r="D4486" s="15">
+        <v>16.8</v>
+      </c>
+      <c r="E4486" s="15">
+        <v>9.5</v>
+      </c>
+      <c r="F4486" s="15">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4487" s="2">
         <v>46125</v>
       </c>
-    </row>
-    <row r="4488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4487" s="12">
+        <v>77235488</v>
+      </c>
+      <c r="C4487" s="12">
+        <v>1806690</v>
+      </c>
+      <c r="D4487" s="15">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E4487" s="15">
+        <v>8.9</v>
+      </c>
+      <c r="F4487" s="15">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4488" s="2">
         <v>46126</v>
       </c>
-    </row>
-    <row r="4489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4488" s="12">
+        <v>90753604</v>
+      </c>
+      <c r="C4488" s="12">
+        <v>2124558</v>
+      </c>
+      <c r="D4488" s="15">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E4488" s="15">
+        <v>10.9</v>
+      </c>
+      <c r="F4488" s="15">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4489" s="2">
         <v>46127</v>
       </c>
-    </row>
-    <row r="4490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4489" s="12">
+        <v>98085135</v>
+      </c>
+      <c r="C4489" s="12">
+        <v>2295829</v>
+      </c>
+      <c r="D4489" s="15">
+        <v>14.7</v>
+      </c>
+      <c r="E4489" s="15">
+        <v>12.7</v>
+      </c>
+      <c r="F4489" s="15">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4490" s="2">
         <v>46128</v>
       </c>
     </row>
-    <row r="4491" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4491" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4491" s="2">
         <v>46129</v>
       </c>
     </row>
-    <row r="4492" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4492" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4492" s="2">
         <v>46130</v>
       </c>
     </row>
-    <row r="4493" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4493" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4493" s="2">
         <v>46131</v>
       </c>
     </row>
-    <row r="4494" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4494" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4494" s="2">
         <v>46132</v>
       </c>
     </row>
-    <row r="4495" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4495" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4495" s="2">
         <v>46133</v>
       </c>
     </row>
-    <row r="4496" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4496" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4496" s="2">
         <v>46134</v>
       </c>

--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1555C2E-7A5A-4473-93C8-6CCB58B57719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2ED7A9D-3269-48E1-A410-66699D5B9F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
   <sheets>
     <sheet name="raw" sheetId="1" r:id="rId1"/>
@@ -89970,13 +89970,13 @@
       <c r="C4444" s="12">
         <v>3620962</v>
       </c>
-      <c r="D4444" s="13">
+      <c r="D4444" s="15">
         <v>8.1</v>
       </c>
-      <c r="E4444" s="13">
+      <c r="E4444" s="15">
         <v>6.7</v>
       </c>
-      <c r="F4444" s="13">
+      <c r="F4444" s="15">
         <v>9.6</v>
       </c>
     </row>
@@ -89990,13 +89990,13 @@
       <c r="C4445" s="12">
         <v>4176814</v>
       </c>
-      <c r="D4445" s="13">
+      <c r="D4445" s="15">
         <v>6.7</v>
       </c>
-      <c r="E4445" s="13">
+      <c r="E4445" s="15">
         <v>4.2</v>
       </c>
-      <c r="F4445" s="13">
+      <c r="F4445" s="15">
         <v>8.1</v>
       </c>
     </row>
@@ -90010,13 +90010,13 @@
       <c r="C4446" s="12">
         <v>4323057</v>
       </c>
-      <c r="D4446" s="13">
+      <c r="D4446" s="15">
         <v>7.4</v>
       </c>
-      <c r="E4446" s="13">
+      <c r="E4446" s="15">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F4446" s="13">
+      <c r="F4446" s="15">
         <v>12.4</v>
       </c>
     </row>
@@ -90030,13 +90030,13 @@
       <c r="C4447" s="12">
         <v>4010199</v>
       </c>
-      <c r="D4447" s="13">
+      <c r="D4447" s="15">
         <v>7.9</v>
       </c>
-      <c r="E4447" s="13">
+      <c r="E4447" s="15">
         <v>2</v>
       </c>
-      <c r="F4447" s="13">
+      <c r="F4447" s="15">
         <v>14</v>
       </c>
     </row>
@@ -90045,18 +90045,18 @@
         <v>46086</v>
       </c>
       <c r="B4448" s="12">
-        <v>171944727</v>
+        <v>171944717</v>
       </c>
       <c r="C4448" s="12">
         <v>3993682</v>
       </c>
-      <c r="D4448" s="13">
+      <c r="D4448" s="15">
         <v>8</v>
       </c>
-      <c r="E4448" s="13">
+      <c r="E4448" s="15">
         <v>1</v>
       </c>
-      <c r="F4448" s="13">
+      <c r="F4448" s="15">
         <v>15</v>
       </c>
     </row>
@@ -90070,13 +90070,13 @@
       <c r="C4449" s="12">
         <v>4174418</v>
       </c>
-      <c r="D4449" s="13">
+      <c r="D4449" s="15">
         <v>6</v>
       </c>
-      <c r="E4449" s="13">
+      <c r="E4449" s="15">
         <v>1.9</v>
       </c>
-      <c r="F4449" s="13">
+      <c r="F4449" s="15">
         <v>9.6</v>
       </c>
     </row>
@@ -90090,13 +90090,13 @@
       <c r="C4450" s="12">
         <v>4135158</v>
       </c>
-      <c r="D4450" s="13">
+      <c r="D4450" s="15">
         <v>3.7</v>
       </c>
-      <c r="E4450" s="13">
+      <c r="E4450" s="15">
         <v>0.1</v>
       </c>
-      <c r="F4450" s="13">
+      <c r="F4450" s="15">
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -90110,13 +90110,13 @@
       <c r="C4451" s="12">
         <v>3942007</v>
       </c>
-      <c r="D4451" s="13">
+      <c r="D4451" s="15">
         <v>4.7</v>
       </c>
-      <c r="E4451" s="13">
+      <c r="E4451" s="15">
         <v>-3.8</v>
       </c>
-      <c r="F4451" s="13">
+      <c r="F4451" s="15">
         <v>12.2</v>
       </c>
     </row>
@@ -90130,13 +90130,13 @@
       <c r="C4452" s="12">
         <v>4551875</v>
       </c>
-      <c r="D4452" s="13">
+      <c r="D4452" s="15">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E4452" s="13">
+      <c r="E4452" s="15">
         <v>1.9</v>
       </c>
-      <c r="F4452" s="13">
+      <c r="F4452" s="15">
         <v>9.1</v>
       </c>
     </row>
@@ -90150,13 +90150,13 @@
       <c r="C4453" s="12">
         <v>4422645</v>
       </c>
-      <c r="D4453" s="13">
+      <c r="D4453" s="15">
         <v>5</v>
       </c>
-      <c r="E4453" s="13">
+      <c r="E4453" s="15">
         <v>-2.1</v>
       </c>
-      <c r="F4453" s="13">
+      <c r="F4453" s="15">
         <v>12.5</v>
       </c>
     </row>
@@ -90170,13 +90170,13 @@
       <c r="C4454" s="12">
         <v>4237626</v>
       </c>
-      <c r="D4454" s="13">
+      <c r="D4454" s="15">
         <v>6.7</v>
       </c>
-      <c r="E4454" s="13">
+      <c r="E4454" s="15">
         <v>-0.6</v>
       </c>
-      <c r="F4454" s="13">
+      <c r="F4454" s="15">
         <v>14.2</v>
       </c>
     </row>
@@ -90190,13 +90190,13 @@
       <c r="C4455" s="12">
         <v>4270524</v>
       </c>
-      <c r="D4455" s="13">
+      <c r="D4455" s="15">
         <v>6.9</v>
       </c>
-      <c r="E4455" s="13">
+      <c r="E4455" s="15">
         <v>1.5</v>
       </c>
-      <c r="F4455" s="13">
+      <c r="F4455" s="15">
         <v>12.3</v>
       </c>
     </row>
@@ -90210,13 +90210,13 @@
       <c r="C4456" s="12">
         <v>4344503</v>
       </c>
-      <c r="D4456" s="13">
+      <c r="D4456" s="15">
         <v>5.6</v>
       </c>
-      <c r="E4456" s="13">
+      <c r="E4456" s="15">
         <v>1.9</v>
       </c>
-      <c r="F4456" s="13">
+      <c r="F4456" s="15">
         <v>10</v>
       </c>
     </row>
@@ -90230,13 +90230,13 @@
       <c r="C4457" s="12">
         <v>3774073</v>
       </c>
-      <c r="D4457" s="13">
+      <c r="D4457" s="15">
         <v>6.7</v>
       </c>
-      <c r="E4457" s="13">
+      <c r="E4457" s="15">
         <v>-1.7</v>
       </c>
-      <c r="F4457" s="13">
+      <c r="F4457" s="15">
         <v>14.8</v>
       </c>
     </row>
@@ -90250,13 +90250,13 @@
       <c r="C4458" s="12">
         <v>3583871</v>
       </c>
-      <c r="D4458" s="13">
+      <c r="D4458" s="15">
         <v>7.8</v>
       </c>
-      <c r="E4458" s="13">
+      <c r="E4458" s="15">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F4458" s="13">
+      <c r="F4458" s="15">
         <v>11.1</v>
       </c>
     </row>
@@ -90265,19 +90265,19 @@
         <v>46097</v>
       </c>
       <c r="B4459" s="12">
-        <v>152227505</v>
+        <v>161279488</v>
       </c>
       <c r="C4459" s="12">
-        <v>3583871</v>
+        <v>3799006</v>
       </c>
       <c r="D4459" s="15">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="E4459" s="15">
-        <v>4.5999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="F4459" s="15">
-        <v>11.1</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="4460" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90285,19 +90285,19 @@
         <v>46098</v>
       </c>
       <c r="B4460" s="12">
-        <v>161279488</v>
+        <v>149887477</v>
       </c>
       <c r="C4460" s="12">
-        <v>3799006</v>
+        <v>3526083</v>
       </c>
       <c r="D4460" s="15">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="E4460" s="15">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="F4460" s="15">
-        <v>16.399999999999999</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="4461" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90305,19 +90305,19 @@
         <v>46099</v>
       </c>
       <c r="B4461" s="12">
-        <v>149887477</v>
+        <v>161055628</v>
       </c>
       <c r="C4461" s="12">
-        <v>3526083</v>
+        <v>3796787</v>
       </c>
       <c r="D4461" s="15">
-        <v>10.8</v>
+        <v>8.6</v>
       </c>
       <c r="E4461" s="15">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="F4461" s="15">
-        <v>18.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="4462" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90325,19 +90325,19 @@
         <v>46100</v>
       </c>
       <c r="B4462" s="12">
-        <v>161055628</v>
+        <v>154958138</v>
       </c>
       <c r="C4462" s="12">
-        <v>3796787</v>
+        <v>3646994</v>
       </c>
       <c r="D4462" s="15">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="E4462" s="15">
-        <v>6.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F4462" s="15">
-        <v>10.7</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="4463" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90345,19 +90345,19 @@
         <v>46101</v>
       </c>
       <c r="B4463" s="12">
-        <v>154958138</v>
+        <v>149312872</v>
       </c>
       <c r="C4463" s="12">
-        <v>3646994</v>
+        <v>3514151</v>
       </c>
       <c r="D4463" s="15">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="E4463" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F4463" s="15">
-        <v>15.7</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="4464" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90365,19 +90365,19 @@
         <v>46102</v>
       </c>
       <c r="B4464" s="12">
-        <v>149312872</v>
+        <v>127022204</v>
       </c>
       <c r="C4464" s="12">
-        <v>3514151</v>
+        <v>2981501</v>
       </c>
       <c r="D4464" s="15">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="E4464" s="15">
-        <v>4.0999999999999996</v>
+        <v>2</v>
       </c>
       <c r="F4464" s="15">
-        <v>17.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4465" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90385,19 +90385,19 @@
         <v>46103</v>
       </c>
       <c r="B4465" s="12">
-        <v>127022204</v>
+        <v>115810115</v>
       </c>
       <c r="C4465" s="12">
-        <v>2981501</v>
+        <v>2712255</v>
       </c>
       <c r="D4465" s="15">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="E4465" s="15">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="F4465" s="15">
-        <v>19.3</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="4466" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90405,19 +90405,19 @@
         <v>46104</v>
       </c>
       <c r="B4466" s="12">
-        <v>115810115</v>
+        <v>131331642</v>
       </c>
       <c r="C4466" s="12">
-        <v>2712255</v>
+        <v>3067061</v>
       </c>
       <c r="D4466" s="15">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4466" s="15">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="F4466" s="15">
-        <v>19.399999999999999</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="4467" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90425,19 +90425,19 @@
         <v>46105</v>
       </c>
       <c r="B4467" s="12">
-        <v>131331642</v>
+        <v>131675317</v>
       </c>
       <c r="C4467" s="12">
-        <v>3067061</v>
+        <v>3072834</v>
       </c>
       <c r="D4467" s="15">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="E4467" s="15">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="F4467" s="15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4468" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90445,19 +90445,19 @@
         <v>46106</v>
       </c>
       <c r="B4468" s="12">
-        <v>131675317</v>
+        <v>126808040</v>
       </c>
       <c r="C4468" s="12">
-        <v>3072834</v>
+        <v>2961328</v>
       </c>
       <c r="D4468" s="15">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
       <c r="E4468" s="15">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="F4468" s="15">
-        <v>19</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="4469" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90465,19 +90465,19 @@
         <v>46107</v>
       </c>
       <c r="B4469" s="12">
-        <v>126808040</v>
+        <v>119607143</v>
       </c>
       <c r="C4469" s="12">
-        <v>2961328</v>
+        <v>2794135</v>
       </c>
       <c r="D4469" s="15">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="E4469" s="15">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="F4469" s="15">
-        <v>18.399999999999999</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="4470" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90485,19 +90485,19 @@
         <v>46108</v>
       </c>
       <c r="B4470" s="12">
-        <v>119607143</v>
+        <v>110740660</v>
       </c>
       <c r="C4470" s="12">
-        <v>2794135</v>
+        <v>2587341</v>
       </c>
       <c r="D4470" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4470" s="15">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="F4470" s="15">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="4471" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90505,19 +90505,19 @@
         <v>46109</v>
       </c>
       <c r="B4471" s="12">
-        <v>110740660</v>
+        <v>92493702</v>
       </c>
       <c r="C4471" s="12">
-        <v>2587341</v>
+        <v>2162203</v>
       </c>
       <c r="D4471" s="15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="E4471" s="15">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="F4471" s="15">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="4472" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90525,19 +90525,19 @@
         <v>46110</v>
       </c>
       <c r="B4472" s="12">
-        <v>92493702</v>
+        <v>84512783</v>
       </c>
       <c r="C4472" s="12">
-        <v>2162203</v>
+        <v>1975528</v>
       </c>
       <c r="D4472" s="15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E4472" s="15">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="F4472" s="15">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="4473" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90545,19 +90545,19 @@
         <v>46111</v>
       </c>
       <c r="B4473" s="12">
-        <v>84512783</v>
+        <v>108455150</v>
       </c>
       <c r="C4473" s="12">
-        <v>1975528</v>
+        <v>2534255</v>
       </c>
       <c r="D4473" s="15">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="E4473" s="15">
-        <v>7.2</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F4473" s="15">
-        <v>22.8</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4474" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90565,19 +90565,19 @@
         <v>46112</v>
       </c>
       <c r="B4474" s="12">
-        <v>108455150</v>
+        <v>116253815</v>
       </c>
       <c r="C4474" s="12">
-        <v>2534255</v>
+        <v>2722597</v>
       </c>
       <c r="D4474" s="15">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="E4474" s="15">
-        <v>9.3000000000000007</v>
+        <v>10.4</v>
       </c>
       <c r="F4474" s="15">
-        <v>19.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4475" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90585,19 +90585,19 @@
         <v>46113</v>
       </c>
       <c r="B4475" s="12">
-        <v>116253815</v>
+        <v>113163968</v>
       </c>
       <c r="C4475" s="12">
-        <v>2722597</v>
+        <v>2657097</v>
       </c>
       <c r="D4475" s="15">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="E4475" s="15">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="F4475" s="15">
-        <v>15.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4476" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90605,19 +90605,19 @@
         <v>46114</v>
       </c>
       <c r="B4476" s="12">
-        <v>113163968</v>
+        <v>110028996</v>
       </c>
       <c r="C4476" s="12">
-        <v>2657097</v>
+        <v>2589721</v>
       </c>
       <c r="D4476" s="15">
-        <v>13.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4476" s="15">
-        <v>10.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F4476" s="15">
-        <v>17</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="4477" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90625,19 +90625,19 @@
         <v>46115</v>
       </c>
       <c r="B4477" s="12">
-        <v>110028996</v>
+        <v>103998595</v>
       </c>
       <c r="C4477" s="12">
-        <v>2589721</v>
+        <v>2447428</v>
       </c>
       <c r="D4477" s="15">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="E4477" s="15">
-        <v>8.1999999999999993</v>
+        <v>6.7</v>
       </c>
       <c r="F4477" s="15">
-        <v>20.7</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="4478" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90645,19 +90645,19 @@
         <v>46116</v>
       </c>
       <c r="B4478" s="12">
-        <v>103998595</v>
+        <v>93885823</v>
       </c>
       <c r="C4478" s="12">
-        <v>2447428</v>
+        <v>2208762</v>
       </c>
       <c r="D4478" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4478" s="15">
-        <v>6.7</v>
+        <v>10.7</v>
       </c>
       <c r="F4478" s="15">
-        <v>23.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4479" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90665,19 +90665,19 @@
         <v>46117</v>
       </c>
       <c r="B4479" s="12">
-        <v>93885823</v>
+        <v>84016293</v>
       </c>
       <c r="C4479" s="12">
-        <v>2208762</v>
+        <v>1982207</v>
       </c>
       <c r="D4479" s="15">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="E4479" s="15">
-        <v>10.7</v>
+        <v>8.4</v>
       </c>
       <c r="F4479" s="15">
-        <v>19</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="4480" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90685,19 +90685,19 @@
         <v>46118</v>
       </c>
       <c r="B4480" s="12">
-        <v>84016293</v>
+        <v>114348356</v>
       </c>
       <c r="C4480" s="12">
-        <v>1982207</v>
+        <v>2687323</v>
       </c>
       <c r="D4480" s="15">
-        <v>14.2</v>
+        <v>11.5</v>
       </c>
       <c r="E4480" s="15">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="F4480" s="15">
-        <v>20.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="4481" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90705,19 +90705,19 @@
         <v>46119</v>
       </c>
       <c r="B4481" s="12">
-        <v>114348356</v>
+        <v>124845506</v>
       </c>
       <c r="C4481" s="12">
-        <v>2687323</v>
+        <v>2926523</v>
       </c>
       <c r="D4481" s="15">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="E4481" s="15">
-        <v>9.5</v>
+        <v>6.2</v>
       </c>
       <c r="F4481" s="15">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="4482" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90725,19 +90725,19 @@
         <v>46120</v>
       </c>
       <c r="B4482" s="12">
-        <v>124845506</v>
+        <v>120297821</v>
       </c>
       <c r="C4482" s="12">
-        <v>2926523</v>
+        <v>2821860</v>
       </c>
       <c r="D4482" s="15">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="E4482" s="15">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="F4482" s="15">
-        <v>15.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="4483" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90745,19 +90745,19 @@
         <v>46121</v>
       </c>
       <c r="B4483" s="12">
-        <v>120297821</v>
+        <v>123067538</v>
       </c>
       <c r="C4483" s="12">
-        <v>2821860</v>
+        <v>2885559</v>
       </c>
       <c r="D4483" s="15">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="E4483" s="15">
-        <v>2.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F4483" s="15">
-        <v>20.9</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="4484" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90765,19 +90765,19 @@
         <v>46122</v>
       </c>
       <c r="B4484" s="12">
-        <v>123067538</v>
+        <v>105864719</v>
       </c>
       <c r="C4484" s="12">
-        <v>2885559</v>
+        <v>2479759</v>
       </c>
       <c r="D4484" s="15">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4484" s="15">
         <v>12.6</v>
       </c>
-      <c r="E4484" s="15">
-        <v>9.3000000000000007</v>
-      </c>
       <c r="F4484" s="15">
-        <v>15.4</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="4485" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90785,19 +90785,19 @@
         <v>46123</v>
       </c>
       <c r="B4485" s="12">
-        <v>105864719</v>
+        <v>87897087</v>
       </c>
       <c r="C4485" s="12">
-        <v>2479759</v>
+        <v>2058917</v>
       </c>
       <c r="D4485" s="15">
-        <v>16.399999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="E4485" s="15">
-        <v>12.6</v>
+        <v>9.5</v>
       </c>
       <c r="F4485" s="15">
-        <v>20.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4486" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90805,19 +90805,19 @@
         <v>46124</v>
       </c>
       <c r="B4486" s="12">
-        <v>87897087</v>
+        <v>77235488</v>
       </c>
       <c r="C4486" s="12">
-        <v>2058917</v>
+        <v>1806690</v>
       </c>
       <c r="D4486" s="15">
-        <v>16.8</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E4486" s="15">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="F4486" s="15">
-        <v>24.9</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4487" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90825,19 +90825,19 @@
         <v>46125</v>
       </c>
       <c r="B4487" s="12">
-        <v>77235488</v>
+        <v>90753604</v>
       </c>
       <c r="C4487" s="12">
-        <v>1806690</v>
+        <v>2124558</v>
       </c>
       <c r="D4487" s="15">
-        <v>16.899999999999999</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E4487" s="15">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="F4487" s="15">
-        <v>23.3</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="4488" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -90845,40 +90845,30 @@
         <v>46126</v>
       </c>
       <c r="B4488" s="12">
-        <v>90753604</v>
+        <v>98085135</v>
       </c>
       <c r="C4488" s="12">
-        <v>2124558</v>
+        <v>2295829</v>
       </c>
       <c r="D4488" s="15">
-        <v>17.600000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="E4488" s="15">
-        <v>10.9</v>
+        <v>12.7</v>
       </c>
       <c r="F4488" s="15">
-        <v>24.3</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="4489" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4489" s="2">
         <v>46127</v>
       </c>
-      <c r="B4489" s="12">
-        <v>98085135</v>
-      </c>
-      <c r="C4489" s="12">
-        <v>2295829</v>
-      </c>
-      <c r="D4489" s="15">
-        <v>14.7</v>
-      </c>
-      <c r="E4489" s="15">
-        <v>12.7</v>
-      </c>
-      <c r="F4489" s="15">
-        <v>17.5</v>
-      </c>
+      <c r="B4489" s="12"/>
+      <c r="C4489" s="12"/>
+      <c r="D4489" s="15"/>
+      <c r="E4489" s="15"/>
+      <c r="F4489" s="15"/>
     </row>
     <row r="4490" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4490" s="2">

--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2ED7A9D-3269-48E1-A410-66699D5B9F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73969A1B-6B2B-4926-B8E0-E9D0F7C3C34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
@@ -420,7 +420,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -559,6 +559,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -736,6 +758,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -90561,27 +90595,27 @@
       </c>
     </row>
     <row r="4474" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4474" s="3">
+      <c r="A4474" s="2">
         <v>46112</v>
       </c>
-      <c r="B4474" s="12">
+      <c r="B4474" s="16">
         <v>116253815</v>
       </c>
-      <c r="C4474" s="12">
+      <c r="C4474" s="16">
         <v>2722597</v>
       </c>
-      <c r="D4474" s="15">
+      <c r="D4474" s="17">
         <v>12.9</v>
       </c>
-      <c r="E4474" s="15">
+      <c r="E4474" s="17">
         <v>10.4</v>
       </c>
-      <c r="F4474" s="15">
+      <c r="F4474" s="17">
         <v>15.8</v>
       </c>
     </row>
     <row r="4475" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4475" s="2">
+      <c r="A4475" s="18">
         <v>46113</v>
       </c>
       <c r="B4475" s="12">
@@ -90590,13 +90624,13 @@
       <c r="C4475" s="12">
         <v>2657097</v>
       </c>
-      <c r="D4475" s="15">
+      <c r="D4475" s="13">
         <v>13.1</v>
       </c>
-      <c r="E4475" s="15">
+      <c r="E4475" s="13">
         <v>10.1</v>
       </c>
-      <c r="F4475" s="15">
+      <c r="F4475" s="13">
         <v>17</v>
       </c>
     </row>
@@ -90610,13 +90644,13 @@
       <c r="C4476" s="12">
         <v>2589721</v>
       </c>
-      <c r="D4476" s="15">
+      <c r="D4476" s="13">
         <v>14.4</v>
       </c>
-      <c r="E4476" s="15">
+      <c r="E4476" s="13">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F4476" s="15">
+      <c r="F4476" s="13">
         <v>20.7</v>
       </c>
     </row>
@@ -90630,13 +90664,13 @@
       <c r="C4477" s="12">
         <v>2447428</v>
       </c>
-      <c r="D4477" s="15">
+      <c r="D4477" s="13">
         <v>15</v>
       </c>
-      <c r="E4477" s="15">
+      <c r="E4477" s="13">
         <v>6.7</v>
       </c>
-      <c r="F4477" s="15">
+      <c r="F4477" s="13">
         <v>23.5</v>
       </c>
     </row>
@@ -90650,13 +90684,13 @@
       <c r="C4478" s="12">
         <v>2208762</v>
       </c>
-      <c r="D4478" s="15">
+      <c r="D4478" s="13">
         <v>14</v>
       </c>
-      <c r="E4478" s="15">
+      <c r="E4478" s="13">
         <v>10.7</v>
       </c>
-      <c r="F4478" s="15">
+      <c r="F4478" s="13">
         <v>19</v>
       </c>
     </row>
@@ -90670,13 +90704,13 @@
       <c r="C4479" s="12">
         <v>1982207</v>
       </c>
-      <c r="D4479" s="15">
+      <c r="D4479" s="13">
         <v>14.2</v>
       </c>
-      <c r="E4479" s="15">
+      <c r="E4479" s="13">
         <v>8.4</v>
       </c>
-      <c r="F4479" s="15">
+      <c r="F4479" s="13">
         <v>20.9</v>
       </c>
     </row>
@@ -90690,13 +90724,13 @@
       <c r="C4480" s="12">
         <v>2687323</v>
       </c>
-      <c r="D4480" s="15">
+      <c r="D4480" s="13">
         <v>11.5</v>
       </c>
-      <c r="E4480" s="15">
+      <c r="E4480" s="13">
         <v>9.5</v>
       </c>
-      <c r="F4480" s="15">
+      <c r="F4480" s="13">
         <v>14.1</v>
       </c>
     </row>
@@ -90710,13 +90744,13 @@
       <c r="C4481" s="12">
         <v>2926523</v>
       </c>
-      <c r="D4481" s="15">
+      <c r="D4481" s="13">
         <v>10.4</v>
       </c>
-      <c r="E4481" s="15">
+      <c r="E4481" s="13">
         <v>6.2</v>
       </c>
-      <c r="F4481" s="15">
+      <c r="F4481" s="13">
         <v>15.4</v>
       </c>
     </row>
@@ -90730,13 +90764,13 @@
       <c r="C4482" s="12">
         <v>2821860</v>
       </c>
-      <c r="D4482" s="15">
+      <c r="D4482" s="13">
         <v>12</v>
       </c>
-      <c r="E4482" s="15">
+      <c r="E4482" s="13">
         <v>2.1</v>
       </c>
-      <c r="F4482" s="15">
+      <c r="F4482" s="13">
         <v>20.9</v>
       </c>
     </row>
@@ -90750,13 +90784,13 @@
       <c r="C4483" s="12">
         <v>2885559</v>
       </c>
-      <c r="D4483" s="15">
+      <c r="D4483" s="13">
         <v>12.6</v>
       </c>
-      <c r="E4483" s="15">
+      <c r="E4483" s="13">
         <v>9.3000000000000007</v>
       </c>
-      <c r="F4483" s="15">
+      <c r="F4483" s="13">
         <v>15.4</v>
       </c>
     </row>
@@ -90770,13 +90804,13 @@
       <c r="C4484" s="12">
         <v>2479759</v>
       </c>
-      <c r="D4484" s="15">
+      <c r="D4484" s="13">
         <v>16.399999999999999</v>
       </c>
-      <c r="E4484" s="15">
+      <c r="E4484" s="13">
         <v>12.6</v>
       </c>
-      <c r="F4484" s="15">
+      <c r="F4484" s="13">
         <v>20.9</v>
       </c>
     </row>
@@ -90790,13 +90824,13 @@
       <c r="C4485" s="12">
         <v>2058917</v>
       </c>
-      <c r="D4485" s="15">
+      <c r="D4485" s="13">
         <v>16.8</v>
       </c>
-      <c r="E4485" s="15">
+      <c r="E4485" s="13">
         <v>9.5</v>
       </c>
-      <c r="F4485" s="15">
+      <c r="F4485" s="13">
         <v>24.9</v>
       </c>
     </row>
@@ -90810,13 +90844,13 @@
       <c r="C4486" s="12">
         <v>1806690</v>
       </c>
-      <c r="D4486" s="15">
+      <c r="D4486" s="13">
         <v>16.899999999999999</v>
       </c>
-      <c r="E4486" s="15">
+      <c r="E4486" s="13">
         <v>8.9</v>
       </c>
-      <c r="F4486" s="15">
+      <c r="F4486" s="13">
         <v>23.3</v>
       </c>
     </row>
@@ -90830,13 +90864,13 @@
       <c r="C4487" s="12">
         <v>2124558</v>
       </c>
-      <c r="D4487" s="15">
+      <c r="D4487" s="13">
         <v>17.600000000000001</v>
       </c>
-      <c r="E4487" s="15">
+      <c r="E4487" s="13">
         <v>10.9</v>
       </c>
-      <c r="F4487" s="15">
+      <c r="F4487" s="13">
         <v>24.3</v>
       </c>
     </row>
@@ -90850,13 +90884,13 @@
       <c r="C4488" s="12">
         <v>2295829</v>
       </c>
-      <c r="D4488" s="15">
+      <c r="D4488" s="13">
         <v>14.7</v>
       </c>
-      <c r="E4488" s="15">
+      <c r="E4488" s="13">
         <v>12.7</v>
       </c>
-      <c r="F4488" s="15">
+      <c r="F4488" s="13">
         <v>17.5</v>
       </c>
     </row>
@@ -90864,683 +90898,2553 @@
       <c r="A4489" s="2">
         <v>46127</v>
       </c>
-      <c r="B4489" s="12"/>
-      <c r="C4489" s="12"/>
-      <c r="D4489" s="15"/>
-      <c r="E4489" s="15"/>
-      <c r="F4489" s="15"/>
-    </row>
-    <row r="4490" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4489" s="12">
+        <v>94892096</v>
+      </c>
+      <c r="C4489" s="12">
+        <v>2222650</v>
+      </c>
+      <c r="D4489" s="13">
+        <v>16.5</v>
+      </c>
+      <c r="E4489" s="13">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F4489" s="13">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4490" s="2">
         <v>46128</v>
       </c>
-    </row>
-    <row r="4491" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4490" s="12">
+        <v>95845997</v>
+      </c>
+      <c r="C4490" s="12">
+        <v>2241765</v>
+      </c>
+      <c r="D4490" s="13">
+        <v>14.4</v>
+      </c>
+      <c r="E4490" s="13">
+        <v>9.1</v>
+      </c>
+      <c r="F4490" s="13">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4491" s="2">
         <v>46129</v>
       </c>
-    </row>
-    <row r="4492" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4491" s="12">
+        <v>100924929</v>
+      </c>
+      <c r="C4491" s="12">
+        <v>2360866</v>
+      </c>
+      <c r="D4491" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="E4491" s="13">
+        <v>10.7</v>
+      </c>
+      <c r="F4491" s="13">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4492" s="2">
         <v>46130</v>
       </c>
-    </row>
-    <row r="4493" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4492" s="12">
+        <v>79593940</v>
+      </c>
+      <c r="C4492" s="12">
+        <v>1858148</v>
+      </c>
+      <c r="D4492" s="13">
+        <v>17.3</v>
+      </c>
+      <c r="E4492" s="13">
+        <v>12.8</v>
+      </c>
+      <c r="F4492" s="13">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4493" s="2">
         <v>46131</v>
       </c>
-    </row>
-    <row r="4494" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4493" s="12">
+        <v>67135173</v>
+      </c>
+      <c r="C4493" s="12">
+        <v>1565203</v>
+      </c>
+      <c r="D4493" s="13">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E4493" s="13">
+        <v>13.6</v>
+      </c>
+      <c r="F4493" s="13">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4494" s="2">
         <v>46132</v>
       </c>
-    </row>
-    <row r="4495" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4494" s="12">
+        <v>85632607</v>
+      </c>
+      <c r="C4494" s="12">
+        <v>1999098</v>
+      </c>
+      <c r="D4494" s="13">
+        <v>17.2</v>
+      </c>
+      <c r="E4494" s="13">
+        <v>10.3</v>
+      </c>
+      <c r="F4494" s="13">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4495" s="2">
         <v>46133</v>
       </c>
-    </row>
-    <row r="4496" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4495" s="12">
+        <v>91382632</v>
+      </c>
+      <c r="C4495" s="12">
+        <v>2133311</v>
+      </c>
+      <c r="D4495" s="13">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E4495" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="F4495" s="13">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4496" s="2">
         <v>46134</v>
       </c>
-    </row>
-    <row r="4497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4496" s="12">
+        <v>92196518</v>
+      </c>
+      <c r="C4496" s="12">
+        <v>2154949</v>
+      </c>
+      <c r="D4496" s="13">
+        <v>15.5</v>
+      </c>
+      <c r="E4496" s="13">
+        <v>12.4</v>
+      </c>
+      <c r="F4496" s="13">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4497" s="2">
         <v>46135</v>
       </c>
-    </row>
-    <row r="4498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4497" s="12">
+        <v>93499387</v>
+      </c>
+      <c r="C4497" s="12">
+        <v>2190634</v>
+      </c>
+      <c r="D4497" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="E4497" s="13">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F4497" s="13">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4498" s="2">
         <v>46136</v>
       </c>
-    </row>
-    <row r="4499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4498" s="12">
+        <v>90626436</v>
+      </c>
+      <c r="C4498" s="12">
+        <v>2126808</v>
+      </c>
+      <c r="D4498" s="13">
+        <v>14.1</v>
+      </c>
+      <c r="E4498" s="13">
+        <v>6.6</v>
+      </c>
+      <c r="F4498" s="13">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4499" s="2">
         <v>46137</v>
       </c>
-    </row>
-    <row r="4500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4499" s="12">
+        <v>75915830</v>
+      </c>
+      <c r="C4499" s="12">
+        <v>1781209</v>
+      </c>
+      <c r="D4499" s="13">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4499" s="13">
+        <v>5.9</v>
+      </c>
+      <c r="F4499" s="13">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4500" s="2">
         <v>46138</v>
       </c>
-    </row>
-    <row r="4501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4500" s="12">
+        <v>64639199</v>
+      </c>
+      <c r="C4500" s="12">
+        <v>1515482</v>
+      </c>
+      <c r="D4500" s="13">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E4500" s="13">
+        <v>8.6</v>
+      </c>
+      <c r="F4500" s="13">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4501" s="2">
         <v>46139</v>
       </c>
-    </row>
-    <row r="4502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4501" s="12">
+        <v>79502448</v>
+      </c>
+      <c r="C4501" s="12">
+        <v>1862346</v>
+      </c>
+      <c r="D4501" s="13">
+        <v>19.8</v>
+      </c>
+      <c r="E4501" s="13">
+        <v>12.2</v>
+      </c>
+      <c r="F4501" s="13">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4502" s="2">
         <v>46140</v>
       </c>
-    </row>
-    <row r="4503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4502" s="12">
+        <v>82631232</v>
+      </c>
+      <c r="C4502" s="12">
+        <v>1935235</v>
+      </c>
+      <c r="D4502" s="13">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E4502" s="13">
+        <v>12.7</v>
+      </c>
+      <c r="F4502" s="13">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4503" s="2">
         <v>46141</v>
       </c>
-    </row>
-    <row r="4504" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4504" s="2">
+      <c r="B4503" s="12">
+        <v>85371132</v>
+      </c>
+      <c r="C4503" s="12">
+        <v>1999374</v>
+      </c>
+      <c r="D4503" s="13">
+        <v>15.3</v>
+      </c>
+      <c r="E4503" s="13">
+        <v>11.3</v>
+      </c>
+      <c r="F4503" s="13">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4504" s="3">
         <v>46142</v>
       </c>
-    </row>
-    <row r="4505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4504" s="12">
+        <v>84440898</v>
+      </c>
+      <c r="C4504" s="12">
+        <v>1977759</v>
+      </c>
+      <c r="D4504" s="13">
+        <v>15.3</v>
+      </c>
+      <c r="E4504" s="13">
+        <v>11.9</v>
+      </c>
+      <c r="F4504" s="13">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4505" s="2">
         <v>46143</v>
       </c>
-    </row>
-    <row r="4506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4505" s="19">
+        <v>67561296</v>
+      </c>
+      <c r="C4505" s="19">
+        <v>1582940</v>
+      </c>
+      <c r="D4505" s="13">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E4505" s="13">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F4505" s="13">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4506" s="2">
         <v>46144</v>
       </c>
-    </row>
-    <row r="4507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4506" s="19">
+        <v>61812507</v>
+      </c>
+      <c r="C4506" s="19">
+        <v>1446808</v>
+      </c>
+      <c r="D4506" s="13">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E4506" s="13">
+        <v>11.8</v>
+      </c>
+      <c r="F4506" s="13">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4507" s="2">
         <v>46145</v>
       </c>
-    </row>
-    <row r="4508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4507" s="19">
+        <v>64298422</v>
+      </c>
+      <c r="C4507" s="19">
+        <v>1506533</v>
+      </c>
+      <c r="D4507" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="E4507" s="13">
+        <v>12.1</v>
+      </c>
+      <c r="F4507" s="13">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4508" s="2">
         <v>46146</v>
       </c>
-    </row>
-    <row r="4509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4508" s="19">
+        <v>77863458</v>
+      </c>
+      <c r="C4508" s="19">
+        <v>1825533</v>
+      </c>
+      <c r="D4508" s="13">
+        <v>15.7</v>
+      </c>
+      <c r="E4508" s="13">
+        <v>10.9</v>
+      </c>
+      <c r="F4508" s="13">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4509" s="2">
         <v>46147</v>
       </c>
-    </row>
-    <row r="4510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4509" s="19">
+        <v>76231958</v>
+      </c>
+      <c r="C4509" s="19">
+        <v>1787258</v>
+      </c>
+      <c r="D4509" s="13">
+        <v>16.2</v>
+      </c>
+      <c r="E4509" s="13">
+        <v>6.4</v>
+      </c>
+      <c r="F4509" s="13">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4510" s="2">
         <v>46148</v>
       </c>
-    </row>
-    <row r="4511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4510" s="19">
+        <v>83879517</v>
+      </c>
+      <c r="C4510" s="19">
+        <v>1960286</v>
+      </c>
+      <c r="D4510" s="13">
+        <v>18.7</v>
+      </c>
+      <c r="E4510" s="13">
+        <v>9</v>
+      </c>
+      <c r="F4510" s="13">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4511" s="2">
         <v>46149</v>
       </c>
-    </row>
-    <row r="4512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4511" s="19">
+        <v>82243044</v>
+      </c>
+      <c r="C4511" s="19">
+        <v>1920717</v>
+      </c>
+      <c r="D4511" s="13">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E4511" s="13">
+        <v>12.6</v>
+      </c>
+      <c r="F4511" s="13">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4512" s="2">
         <v>46150</v>
       </c>
-    </row>
-    <row r="4513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4512" s="19">
+        <v>81498487</v>
+      </c>
+      <c r="C4512" s="19">
+        <v>1903955</v>
+      </c>
+      <c r="D4512" s="13">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E4512" s="13">
+        <v>13</v>
+      </c>
+      <c r="F4512" s="13">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4513" s="2">
         <v>46151</v>
       </c>
-    </row>
-    <row r="4514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4513" s="19">
+        <v>67159928</v>
+      </c>
+      <c r="C4513" s="19">
+        <v>1575280</v>
+      </c>
+      <c r="D4513" s="13">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E4513" s="13">
+        <v>7.9</v>
+      </c>
+      <c r="F4513" s="13">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4514" s="2">
         <v>46152</v>
       </c>
-    </row>
-    <row r="4515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4514" s="19">
+        <v>59228738</v>
+      </c>
+      <c r="C4514" s="19">
+        <v>1387703</v>
+      </c>
+      <c r="D4514" s="13">
+        <v>18.8</v>
+      </c>
+      <c r="E4514" s="13">
+        <v>10</v>
+      </c>
+      <c r="F4514" s="13">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4515" s="2">
         <v>46153</v>
       </c>
-    </row>
-    <row r="4516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4515" s="19">
+        <v>75817145</v>
+      </c>
+      <c r="C4515" s="19">
+        <v>1778722</v>
+      </c>
+      <c r="D4515" s="13">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E4515" s="13">
+        <v>11.1</v>
+      </c>
+      <c r="F4515" s="13">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4516" s="2">
         <v>46154</v>
       </c>
-    </row>
-    <row r="4517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4516" s="19">
+        <v>79290316</v>
+      </c>
+      <c r="C4516" s="19">
+        <v>1863287</v>
+      </c>
+      <c r="D4516" s="13">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E4516" s="13">
+        <v>15.2</v>
+      </c>
+      <c r="F4516" s="13">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4517" s="2">
         <v>46155</v>
       </c>
-    </row>
-    <row r="4518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4517" s="19">
+        <v>78804625</v>
+      </c>
+      <c r="C4517" s="19">
+        <v>1854400</v>
+      </c>
+      <c r="D4517" s="13">
+        <v>20.9</v>
+      </c>
+      <c r="E4517" s="13">
+        <v>13</v>
+      </c>
+      <c r="F4517" s="13">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4518" s="2">
         <v>46156</v>
       </c>
-    </row>
-    <row r="4519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4518" s="19">
+        <v>78337578</v>
+      </c>
+      <c r="C4518" s="19">
+        <v>1836812</v>
+      </c>
+      <c r="D4518" s="13">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E4518" s="13">
+        <v>15.2</v>
+      </c>
+      <c r="F4518" s="13">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4519" s="2">
         <v>46157</v>
       </c>
-    </row>
-    <row r="4520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4519" s="19">
+        <v>75987209</v>
+      </c>
+      <c r="C4519" s="19">
+        <v>1783345</v>
+      </c>
+      <c r="D4519" s="13">
+        <v>21.8</v>
+      </c>
+      <c r="E4519" s="13">
+        <v>14</v>
+      </c>
+      <c r="F4519" s="13">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4520" s="2">
         <v>46158</v>
       </c>
-    </row>
-    <row r="4521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4520" s="19">
+        <v>60506291</v>
+      </c>
+      <c r="C4520" s="19">
+        <v>1415941</v>
+      </c>
+      <c r="D4520" s="13">
+        <v>24.1</v>
+      </c>
+      <c r="E4520" s="13">
+        <v>13.7</v>
+      </c>
+      <c r="F4520" s="13">
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4521" s="2">
         <v>46159</v>
       </c>
-    </row>
-    <row r="4522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4521" s="19">
+        <v>53316739</v>
+      </c>
+      <c r="C4521" s="19">
+        <v>1248151</v>
+      </c>
+      <c r="D4521" s="13">
+        <v>25.7</v>
+      </c>
+      <c r="E4521" s="13">
+        <v>15.9</v>
+      </c>
+      <c r="F4521" s="13">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4522" s="2">
         <v>46160</v>
       </c>
-    </row>
-    <row r="4523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4522" s="19">
+        <v>72636073</v>
+      </c>
+      <c r="C4522" s="19">
+        <v>1701846</v>
+      </c>
+      <c r="D4522" s="1">
+        <v>25.3</v>
+      </c>
+      <c r="E4522" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F4522" s="1">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4523" s="2">
         <v>46161</v>
       </c>
-    </row>
-    <row r="4524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4523" s="19">
+        <v>75215499</v>
+      </c>
+      <c r="C4523" s="19">
+        <v>1762560</v>
+      </c>
+      <c r="D4523" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="E4523" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="F4523" s="1">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4524" s="2">
         <v>46162</v>
       </c>
-    </row>
-    <row r="4525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4524" s="19">
+        <v>77909089</v>
+      </c>
+      <c r="C4524" s="19">
+        <v>1831157</v>
+      </c>
+      <c r="D4524" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="E4524" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="F4524" s="1">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4525" s="2">
         <v>46163</v>
       </c>
-    </row>
-    <row r="4526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4525" s="19">
+        <v>78305064</v>
+      </c>
+      <c r="C4525" s="19">
+        <v>1836692</v>
+      </c>
+      <c r="D4525" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="E4525" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="F4525" s="1">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4526" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="4527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4526" s="19">
+        <v>75830881</v>
+      </c>
+      <c r="C4526" s="19">
+        <v>1781154</v>
+      </c>
+      <c r="D4526" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E4526" s="1">
+        <v>16</v>
+      </c>
+      <c r="F4526" s="1">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4527" s="2">
         <v>46165</v>
       </c>
-    </row>
-    <row r="4528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4527" s="19">
+        <v>62436870</v>
+      </c>
+      <c r="C4527" s="19">
+        <v>1465411</v>
+      </c>
+      <c r="D4527" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="E4527" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="F4527" s="1">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4528" s="2">
         <v>46166</v>
       </c>
-    </row>
-    <row r="4529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4528" s="19">
+        <v>53343258</v>
+      </c>
+      <c r="C4528" s="19">
+        <v>1254634</v>
+      </c>
+      <c r="D4528" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E4528" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="F4528" s="1">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4529" s="2">
         <v>46167</v>
       </c>
-    </row>
-    <row r="4530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4529" s="19">
+        <v>58848814</v>
+      </c>
+      <c r="C4529" s="19">
+        <v>1386683</v>
+      </c>
+      <c r="D4529" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="E4529" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F4529" s="1">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4530" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="4531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4530" s="19">
+        <v>74533624</v>
+      </c>
+      <c r="C4530" s="19">
+        <v>1748969</v>
+      </c>
+      <c r="D4530" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="E4530" s="1">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F4530" s="1">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4531" s="2">
         <v>46169</v>
       </c>
-    </row>
-    <row r="4532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4531" s="19">
+        <v>76359283</v>
+      </c>
+      <c r="C4531" s="19">
+        <v>1796565</v>
+      </c>
+      <c r="D4531" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E4531" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="F4531" s="1">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4532" s="2">
         <v>46170</v>
       </c>
-    </row>
-    <row r="4533" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4532" s="19">
+        <v>77196888</v>
+      </c>
+      <c r="C4532" s="19">
+        <v>1817794</v>
+      </c>
+      <c r="D4532" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="E4532" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F4532" s="1">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4533" s="2">
         <v>46171</v>
       </c>
-    </row>
-    <row r="4534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4533" s="19">
+        <v>73265187</v>
+      </c>
+      <c r="C4533" s="19">
+        <v>1722401</v>
+      </c>
+      <c r="D4533" s="1">
+        <v>23.2</v>
+      </c>
+      <c r="E4533" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="F4533" s="1">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4534" s="2">
         <v>46172</v>
       </c>
-    </row>
-    <row r="4535" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4535" s="2">
+      <c r="B4534" s="19">
+        <v>56581914</v>
+      </c>
+      <c r="C4534" s="19">
+        <v>1331880</v>
+      </c>
+      <c r="D4534" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="E4534" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="F4534" s="1">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4535" s="3">
         <v>46173</v>
       </c>
-    </row>
-    <row r="4536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4535" s="19">
+        <v>50245264</v>
+      </c>
+      <c r="C4535" s="19">
+        <v>1183759</v>
+      </c>
+      <c r="D4535" s="4">
+        <v>25.4</v>
+      </c>
+      <c r="E4535" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="F4535" s="4">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4536" s="2">
         <v>46174</v>
       </c>
-    </row>
-    <row r="4537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4536" s="12">
+        <v>70097118</v>
+      </c>
+      <c r="C4536" s="12">
+        <v>1652099</v>
+      </c>
+      <c r="D4536" s="13">
+        <v>24.8</v>
+      </c>
+      <c r="E4536" s="13">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F4536" s="13">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4537" s="2">
         <v>46175</v>
       </c>
-    </row>
-    <row r="4538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4537" s="12">
+        <v>74487054</v>
+      </c>
+      <c r="C4537" s="12">
+        <v>1752867</v>
+      </c>
+      <c r="D4537" s="13">
+        <v>21.2</v>
+      </c>
+      <c r="E4537" s="13">
+        <v>19.5</v>
+      </c>
+      <c r="F4537" s="13">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4538" s="2">
         <v>46176</v>
       </c>
-    </row>
-    <row r="4539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4538" s="12">
+        <v>60576870</v>
+      </c>
+      <c r="C4538" s="12">
+        <v>1426985</v>
+      </c>
+      <c r="D4538" s="13">
+        <v>23.6</v>
+      </c>
+      <c r="E4538" s="13">
+        <v>17.3</v>
+      </c>
+      <c r="F4538" s="13">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4539" s="2">
         <v>46177</v>
       </c>
-    </row>
-    <row r="4540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4539" s="12">
+        <v>71954079</v>
+      </c>
+      <c r="C4539" s="12">
+        <v>1693663</v>
+      </c>
+      <c r="D4539" s="13">
+        <v>24.1</v>
+      </c>
+      <c r="E4539" s="13">
+        <v>20.2</v>
+      </c>
+      <c r="F4539" s="13">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4540" s="2">
         <v>46178</v>
       </c>
-    </row>
-    <row r="4541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4540" s="12">
+        <v>71447580</v>
+      </c>
+      <c r="C4540" s="12">
+        <v>1685398</v>
+      </c>
+      <c r="D4540" s="13">
+        <v>23.4</v>
+      </c>
+      <c r="E4540" s="13">
+        <v>18.8</v>
+      </c>
+      <c r="F4540" s="13">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4541" s="2">
         <v>46179</v>
       </c>
-    </row>
-    <row r="4542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4541" s="12">
+        <v>53614870</v>
+      </c>
+      <c r="C4541" s="12">
+        <v>1265142</v>
+      </c>
+      <c r="D4541" s="13">
+        <v>22.1</v>
+      </c>
+      <c r="E4541" s="13">
+        <v>14.7</v>
+      </c>
+      <c r="F4541" s="13">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4542" s="2">
         <v>46180</v>
       </c>
-    </row>
-    <row r="4543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4542" s="12">
+        <v>48915766</v>
+      </c>
+      <c r="C4542" s="12">
+        <v>1154089</v>
+      </c>
+      <c r="D4542" s="13">
+        <v>20.8</v>
+      </c>
+      <c r="E4542" s="13">
+        <v>18.5</v>
+      </c>
+      <c r="F4542" s="13">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4543" s="2">
         <v>46181</v>
       </c>
-    </row>
-    <row r="4544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4543" s="12">
+        <v>69894394</v>
+      </c>
+      <c r="C4543" s="12">
+        <v>1650110</v>
+      </c>
+      <c r="D4543" s="13">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E4543" s="13">
+        <v>18</v>
+      </c>
+      <c r="F4543" s="13">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4544" s="2">
         <v>46182</v>
       </c>
-    </row>
-    <row r="4545" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4544" s="12">
+        <v>73399291</v>
+      </c>
+      <c r="C4544" s="12">
+        <v>1731585</v>
+      </c>
+      <c r="D4544" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="E4544" s="13">
+        <v>15.6</v>
+      </c>
+      <c r="F4544" s="13">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4545" s="2">
         <v>46183</v>
       </c>
-    </row>
-    <row r="4546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4545" s="12">
+        <v>72012328</v>
+      </c>
+      <c r="C4545" s="12">
+        <v>1699147</v>
+      </c>
+      <c r="D4545" s="13">
+        <v>23.4</v>
+      </c>
+      <c r="E4545" s="13">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F4545" s="13">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4546" s="2">
         <v>46184</v>
       </c>
-    </row>
-    <row r="4547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4546" s="12">
+        <v>71550154</v>
+      </c>
+      <c r="C4546" s="12">
+        <v>1688053</v>
+      </c>
+      <c r="D4546" s="13">
+        <v>23.1</v>
+      </c>
+      <c r="E4546" s="13">
+        <v>15.9</v>
+      </c>
+      <c r="F4546" s="13">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4547" s="2">
         <v>46185</v>
       </c>
-    </row>
-    <row r="4548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4547" s="12">
+        <v>70115574</v>
+      </c>
+      <c r="C4547" s="12">
+        <v>1657199</v>
+      </c>
+      <c r="D4547" s="13">
+        <v>24.2</v>
+      </c>
+      <c r="E4547" s="13">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F4547" s="13">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4548" s="2">
         <v>46186</v>
       </c>
-    </row>
-    <row r="4549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4548" s="12">
+        <v>55094846</v>
+      </c>
+      <c r="C4548" s="12">
+        <v>1300684</v>
+      </c>
+      <c r="D4548" s="13">
+        <v>25.3</v>
+      </c>
+      <c r="E4548" s="13">
+        <v>17</v>
+      </c>
+      <c r="F4548" s="13">
+        <v>32.700000000000003</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4549" s="2">
         <v>46187</v>
       </c>
-    </row>
-    <row r="4550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4549" s="12">
+        <v>48211550</v>
+      </c>
+      <c r="C4549" s="12">
+        <v>1136147</v>
+      </c>
+      <c r="D4549" s="13">
+        <v>24.4</v>
+      </c>
+      <c r="E4549" s="13">
+        <v>18.8</v>
+      </c>
+      <c r="F4549" s="13">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4550" s="2">
         <v>46188</v>
       </c>
-    </row>
-    <row r="4551" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4550" s="12">
+        <v>68590530</v>
+      </c>
+      <c r="C4550" s="12">
+        <v>1616213</v>
+      </c>
+      <c r="D4550" s="13">
+        <v>24.4</v>
+      </c>
+      <c r="E4550" s="13">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F4550" s="13">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4551" s="2">
         <v>46189</v>
       </c>
-    </row>
-    <row r="4552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4551" s="12">
+        <v>71994730</v>
+      </c>
+      <c r="C4551" s="12">
+        <v>1697677</v>
+      </c>
+      <c r="D4551" s="13">
+        <v>24.3</v>
+      </c>
+      <c r="E4551" s="13">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="F4551" s="13">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4552" s="2">
         <v>46190</v>
       </c>
-    </row>
-    <row r="4553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4552" s="12">
+        <v>71250023</v>
+      </c>
+      <c r="C4552" s="12">
+        <v>1678953</v>
+      </c>
+      <c r="D4552" s="13">
+        <v>26.1</v>
+      </c>
+      <c r="E4552" s="13">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F4552" s="13">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4553" s="2">
         <v>46191</v>
       </c>
-    </row>
-    <row r="4554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4553" s="12">
+        <v>71874014</v>
+      </c>
+      <c r="C4553" s="12">
+        <v>1693478</v>
+      </c>
+      <c r="D4553" s="13">
+        <v>27.1</v>
+      </c>
+      <c r="E4553" s="13">
+        <v>22.3</v>
+      </c>
+      <c r="F4553" s="13">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4554" s="2">
         <v>46192</v>
       </c>
-    </row>
-    <row r="4555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4554" s="12">
+        <v>69413638</v>
+      </c>
+      <c r="C4554" s="12">
+        <v>1634926</v>
+      </c>
+      <c r="D4554" s="13">
+        <v>25.7</v>
+      </c>
+      <c r="E4554" s="13">
+        <v>22.7</v>
+      </c>
+      <c r="F4554" s="13">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4555" s="2">
         <v>46193</v>
       </c>
-    </row>
-    <row r="4556" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4555" s="12">
+        <v>54218739</v>
+      </c>
+      <c r="C4555" s="12">
+        <v>1279199</v>
+      </c>
+      <c r="D4555" s="13">
+        <v>25.9</v>
+      </c>
+      <c r="E4555" s="13">
+        <v>22.2</v>
+      </c>
+      <c r="F4555" s="13">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4556" s="2">
         <v>46194</v>
       </c>
-    </row>
-    <row r="4557" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4556" s="12">
+        <v>47570329</v>
+      </c>
+      <c r="C4556" s="12">
+        <v>1121488</v>
+      </c>
+      <c r="D4556" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="E4556" s="13">
+        <v>20.7</v>
+      </c>
+      <c r="F4556" s="13">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4557" s="2">
         <v>46195</v>
       </c>
-    </row>
-    <row r="4558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4557" s="12">
+        <v>66648267</v>
+      </c>
+      <c r="C4557" s="12">
+        <v>1571991</v>
+      </c>
+      <c r="D4557" s="13">
+        <v>20.7</v>
+      </c>
+      <c r="E4557" s="13">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F4557" s="13">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4558" s="2">
         <v>46196</v>
       </c>
-    </row>
-    <row r="4559" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4558" s="12">
+        <v>72486465</v>
+      </c>
+      <c r="C4558" s="12">
+        <v>1709919</v>
+      </c>
+      <c r="D4558" s="14">
+        <v>19.8</v>
+      </c>
+      <c r="E4558" s="14">
+        <v>17.8</v>
+      </c>
+      <c r="F4558" s="14">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4559" s="2">
         <v>46197</v>
       </c>
-    </row>
-    <row r="4560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4559" s="12">
+        <v>70154961</v>
+      </c>
+      <c r="C4559" s="12">
+        <v>1656412</v>
+      </c>
+      <c r="D4559" s="14">
+        <v>20.8</v>
+      </c>
+      <c r="E4559" s="14">
+        <v>19</v>
+      </c>
+      <c r="F4559" s="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4560" s="2">
         <v>46198</v>
       </c>
-    </row>
-    <row r="4561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4560" s="12">
+        <v>70900693</v>
+      </c>
+      <c r="C4560" s="12">
+        <v>1674106</v>
+      </c>
+      <c r="D4560" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="E4560" s="13">
+        <v>19.5</v>
+      </c>
+      <c r="F4560" s="13">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4561" s="2">
         <v>46199</v>
       </c>
-    </row>
-    <row r="4562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4561" s="12">
+        <v>67345280</v>
+      </c>
+      <c r="C4561" s="12">
+        <v>1590282</v>
+      </c>
+      <c r="D4561" s="13">
+        <v>23.1</v>
+      </c>
+      <c r="E4561" s="13">
+        <v>19</v>
+      </c>
+      <c r="F4561" s="13">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4562" s="2">
         <v>46200</v>
       </c>
-    </row>
-    <row r="4563" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4562" s="12">
+        <v>54190782</v>
+      </c>
+      <c r="C4562" s="12">
+        <v>1279430</v>
+      </c>
+      <c r="D4562" s="13">
+        <v>22.2</v>
+      </c>
+      <c r="E4562" s="13">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F4562" s="13">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4563" s="2">
         <v>46201</v>
       </c>
-    </row>
-    <row r="4564" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4563" s="12">
+        <v>48177961</v>
+      </c>
+      <c r="C4563" s="12">
+        <v>1137941</v>
+      </c>
+      <c r="D4563" s="13">
+        <v>23.6</v>
+      </c>
+      <c r="E4563" s="13">
+        <v>15.4</v>
+      </c>
+      <c r="F4563" s="13">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4564" s="2">
         <v>46202</v>
       </c>
-    </row>
-    <row r="4565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4564" s="12">
+        <v>67005639</v>
+      </c>
+      <c r="C4564" s="12">
+        <v>1583676</v>
+      </c>
+      <c r="D4564" s="13">
+        <v>24.5</v>
+      </c>
+      <c r="E4564" s="13">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F4564" s="13">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4565" s="2">
         <v>46203</v>
       </c>
-    </row>
-    <row r="4566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4565" s="12">
+        <v>69025152</v>
+      </c>
+      <c r="C4565" s="12">
+        <v>1630041</v>
+      </c>
+      <c r="D4565" s="13">
+        <v>25.3</v>
+      </c>
+      <c r="E4565" s="13">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F4565" s="13">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4566" s="2">
         <v>46204</v>
       </c>
-    </row>
-    <row r="4567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4566" s="12">
+        <v>69351788</v>
+      </c>
+      <c r="C4566" s="12">
+        <v>1635670</v>
+      </c>
+      <c r="D4566" s="13">
+        <v>21.3</v>
+      </c>
+      <c r="E4566" s="13">
+        <v>20</v>
+      </c>
+      <c r="F4566" s="13">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4567" s="2">
         <v>46205</v>
       </c>
-    </row>
-    <row r="4568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4567" s="12">
+        <v>70015732</v>
+      </c>
+      <c r="C4567" s="12">
+        <v>1650849</v>
+      </c>
+      <c r="D4567" s="13">
+        <v>24.6</v>
+      </c>
+      <c r="E4567" s="13">
+        <v>19.8</v>
+      </c>
+      <c r="F4567" s="13">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4568" s="2">
         <v>46206</v>
       </c>
-    </row>
-    <row r="4569" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4568" s="12">
+        <v>67991355</v>
+      </c>
+      <c r="C4568" s="12">
+        <v>1604225</v>
+      </c>
+      <c r="D4568" s="13">
+        <v>26</v>
+      </c>
+      <c r="E4568" s="13">
+        <v>22.1</v>
+      </c>
+      <c r="F4568" s="13">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4569" s="2">
         <v>46207</v>
       </c>
-    </row>
-    <row r="4570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4569" s="12">
+        <v>52527637</v>
+      </c>
+      <c r="C4569" s="12">
+        <v>1239564</v>
+      </c>
+      <c r="D4569" s="13">
+        <v>26.6</v>
+      </c>
+      <c r="E4569" s="13">
+        <v>23.2</v>
+      </c>
+      <c r="F4569" s="13">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4570" s="2">
         <v>46208</v>
       </c>
-    </row>
-    <row r="4571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4570" s="12">
+        <v>47880383</v>
+      </c>
+      <c r="C4570" s="12">
+        <v>1129648</v>
+      </c>
+      <c r="D4570" s="13">
+        <v>26</v>
+      </c>
+      <c r="E4570" s="13">
+        <v>23</v>
+      </c>
+      <c r="F4570" s="13">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4571" s="2">
         <v>46209</v>
       </c>
-    </row>
-    <row r="4572" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4571" s="12">
+        <v>65738609</v>
+      </c>
+      <c r="C4571" s="12">
+        <v>1554510</v>
+      </c>
+      <c r="D4571" s="13">
+        <v>28.1</v>
+      </c>
+      <c r="E4571" s="13">
+        <v>23.9</v>
+      </c>
+      <c r="F4571" s="13">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4572" s="2">
         <v>46210</v>
       </c>
-    </row>
-    <row r="4573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4572" s="12">
+        <v>70031811</v>
+      </c>
+      <c r="C4572" s="12">
+        <v>1655065</v>
+      </c>
+      <c r="D4572" s="13">
+        <v>28</v>
+      </c>
+      <c r="E4572" s="13">
+        <v>24.7</v>
+      </c>
+      <c r="F4572" s="13">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4573" s="2">
         <v>46211</v>
       </c>
-    </row>
-    <row r="4574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4573" s="12">
+        <v>68963296</v>
+      </c>
+      <c r="C4573" s="12">
+        <v>1625547</v>
+      </c>
+      <c r="D4573" s="13">
+        <v>28.6</v>
+      </c>
+      <c r="E4573" s="13">
+        <v>25.1</v>
+      </c>
+      <c r="F4573" s="13">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4574" s="2">
         <v>46212</v>
       </c>
-    </row>
-    <row r="4575" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4574" s="12">
+        <v>68763018</v>
+      </c>
+      <c r="C4574" s="12">
+        <v>1620695</v>
+      </c>
+      <c r="D4574" s="13">
+        <v>27.7</v>
+      </c>
+      <c r="E4574" s="13">
+        <v>25.3</v>
+      </c>
+      <c r="F4574" s="13">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4575" s="2">
         <v>46213</v>
       </c>
-    </row>
-    <row r="4576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4575" s="12">
+        <v>66718721</v>
+      </c>
+      <c r="C4575" s="12">
+        <v>1573562</v>
+      </c>
+      <c r="D4575" s="13">
+        <v>29.3</v>
+      </c>
+      <c r="E4575" s="13">
+        <v>24.2</v>
+      </c>
+      <c r="F4575" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4576" s="2">
         <v>46214</v>
       </c>
-    </row>
-    <row r="4577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4576" s="12">
+        <v>51868373</v>
+      </c>
+      <c r="C4576" s="12">
+        <v>1224974</v>
+      </c>
+      <c r="D4576" s="13">
+        <v>30.7</v>
+      </c>
+      <c r="E4576" s="13">
+        <v>23.7</v>
+      </c>
+      <c r="F4576" s="13">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4577" s="2">
         <v>46215</v>
       </c>
-    </row>
-    <row r="4578" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4577" s="12">
+        <v>46580497</v>
+      </c>
+      <c r="C4577" s="12">
+        <v>1100692</v>
+      </c>
+      <c r="D4577" s="13">
+        <v>30.4</v>
+      </c>
+      <c r="E4577" s="13">
+        <v>25.3</v>
+      </c>
+      <c r="F4577" s="13">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4578" s="2">
         <v>46216</v>
       </c>
-    </row>
-    <row r="4579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4578" s="12">
+        <v>64479059</v>
+      </c>
+      <c r="C4578" s="12">
+        <v>1523117</v>
+      </c>
+      <c r="D4578" s="13">
+        <v>30.9</v>
+      </c>
+      <c r="E4578" s="13">
+        <v>27.1</v>
+      </c>
+      <c r="F4578" s="13">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4579" s="2">
         <v>46217</v>
       </c>
-    </row>
-    <row r="4580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4579" s="12">
+        <v>70117710</v>
+      </c>
+      <c r="C4579" s="12">
+        <v>1657641</v>
+      </c>
+      <c r="D4579" s="13">
+        <v>30.1</v>
+      </c>
+      <c r="E4579" s="13">
+        <v>27</v>
+      </c>
+      <c r="F4579" s="13">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4580" s="2">
         <v>46218</v>
       </c>
-    </row>
-    <row r="4581" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4580" s="12">
+        <v>68171782</v>
+      </c>
+      <c r="C4580" s="12">
+        <v>1611933</v>
+      </c>
+      <c r="D4580" s="13">
+        <v>31.4</v>
+      </c>
+      <c r="E4580" s="13">
+        <v>27.7</v>
+      </c>
+      <c r="F4580" s="13">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4581" s="2">
         <v>46219</v>
       </c>
-    </row>
-    <row r="4582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4581" s="12">
+        <v>67007780</v>
+      </c>
+      <c r="C4581" s="12">
+        <v>1584176</v>
+      </c>
+      <c r="D4581" s="13">
+        <v>29.4</v>
+      </c>
+      <c r="E4581" s="13">
+        <v>26</v>
+      </c>
+      <c r="F4581" s="13">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4582" s="2">
         <v>46220</v>
       </c>
-    </row>
-    <row r="4583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4582" s="12">
+        <v>51320383</v>
+      </c>
+      <c r="C4582" s="12">
+        <v>1212087</v>
+      </c>
+      <c r="D4582" s="13">
+        <v>27.6</v>
+      </c>
+      <c r="E4582" s="13">
+        <v>21.9</v>
+      </c>
+      <c r="F4582" s="13">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4583" s="2">
         <v>46221</v>
       </c>
-    </row>
-    <row r="4584" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4583" s="12">
+        <v>47096680</v>
+      </c>
+      <c r="C4583" s="12">
+        <v>1111085</v>
+      </c>
+      <c r="D4583" s="13">
+        <v>27.2</v>
+      </c>
+      <c r="E4583" s="13">
+        <v>21.9</v>
+      </c>
+      <c r="F4583" s="13">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4584" s="2">
         <v>46222</v>
       </c>
-    </row>
-    <row r="4585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4584" s="12">
+        <v>43518312</v>
+      </c>
+      <c r="C4584" s="12">
+        <v>1026346</v>
+      </c>
+      <c r="D4584" s="13">
+        <v>25.6</v>
+      </c>
+      <c r="E4584" s="13">
+        <v>22.5</v>
+      </c>
+      <c r="F4584" s="13">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4585" s="2">
         <v>46223</v>
       </c>
-    </row>
-    <row r="4586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4585" s="12">
+        <v>65018107</v>
+      </c>
+      <c r="C4585" s="12">
+        <v>1534976</v>
+      </c>
+      <c r="D4585" s="13">
+        <v>28.8</v>
+      </c>
+      <c r="E4585" s="13">
+        <v>24.2</v>
+      </c>
+      <c r="F4585" s="13">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4586" s="2">
         <v>46224</v>
       </c>
-    </row>
-    <row r="4587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4586" s="12">
+        <v>67461920</v>
+      </c>
+      <c r="C4586" s="12">
+        <v>1594114</v>
+      </c>
+      <c r="D4586" s="13">
+        <v>30</v>
+      </c>
+      <c r="E4586" s="13">
+        <v>25.3</v>
+      </c>
+      <c r="F4586" s="13">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4587" s="2">
         <v>46225</v>
       </c>
-    </row>
-    <row r="4588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4587" s="12">
+        <v>66763250</v>
+      </c>
+      <c r="C4587" s="12">
+        <v>1575711</v>
+      </c>
+      <c r="D4587" s="13">
+        <v>30.5</v>
+      </c>
+      <c r="E4587" s="13">
+        <v>25.9</v>
+      </c>
+      <c r="F4587" s="13">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4588" s="2">
         <v>46226</v>
       </c>
-    </row>
-    <row r="4589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4588" s="12">
+        <v>67296446</v>
+      </c>
+      <c r="C4588" s="12">
+        <v>1589524</v>
+      </c>
+      <c r="D4588" s="13">
+        <v>30.6</v>
+      </c>
+      <c r="E4588" s="13">
+        <v>25.6</v>
+      </c>
+      <c r="F4588" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4589" s="2">
         <v>46227</v>
       </c>
-    </row>
-    <row r="4590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4589" s="12">
+        <v>64296106</v>
+      </c>
+      <c r="C4589" s="12">
+        <v>1519420</v>
+      </c>
+      <c r="D4589" s="13">
+        <v>31.5</v>
+      </c>
+      <c r="E4589" s="13">
+        <v>26.2</v>
+      </c>
+      <c r="F4589" s="13">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4590" s="2">
         <v>46228</v>
       </c>
-    </row>
-    <row r="4591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4590" s="12">
+        <v>49610488</v>
+      </c>
+      <c r="C4590" s="12">
+        <v>1172674</v>
+      </c>
+      <c r="D4590" s="13">
+        <v>31.1</v>
+      </c>
+      <c r="E4590" s="13">
+        <v>27</v>
+      </c>
+      <c r="F4590" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4591" s="2">
         <v>46229</v>
       </c>
-    </row>
-    <row r="4592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4591" s="12">
+        <v>43006543</v>
+      </c>
+      <c r="C4591" s="12">
+        <v>1015267</v>
+      </c>
+      <c r="D4591" s="13">
+        <v>30.8</v>
+      </c>
+      <c r="E4591" s="13">
+        <v>26.3</v>
+      </c>
+      <c r="F4591" s="13">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4592" s="2">
         <v>46230</v>
       </c>
-    </row>
-    <row r="4593" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4592" s="12">
+        <v>61203219</v>
+      </c>
+      <c r="C4592" s="12">
+        <v>1444252</v>
+      </c>
+      <c r="D4592" s="13">
+        <v>31.1</v>
+      </c>
+      <c r="E4592" s="13">
+        <v>24.8</v>
+      </c>
+      <c r="F4592" s="13">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4593" s="2">
         <v>46231</v>
       </c>
-    </row>
-    <row r="4594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4593" s="12">
+        <v>63239194</v>
+      </c>
+      <c r="C4593" s="12">
+        <v>1493251</v>
+      </c>
+      <c r="D4593" s="13">
+        <v>31.2</v>
+      </c>
+      <c r="E4593" s="13">
+        <v>28</v>
+      </c>
+      <c r="F4593" s="13">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4594" s="2">
         <v>46232</v>
       </c>
-    </row>
-    <row r="4595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4594" s="12">
+        <v>60949080</v>
+      </c>
+      <c r="C4594" s="12">
+        <v>1440072</v>
+      </c>
+      <c r="D4594" s="13">
+        <v>31</v>
+      </c>
+      <c r="E4594" s="13">
+        <v>28</v>
+      </c>
+      <c r="F4594" s="13">
+        <v>35.299999999999997</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4595" s="2">
         <v>46233</v>
       </c>
-    </row>
-    <row r="4596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4595" s="12">
+        <v>58146826</v>
+      </c>
+      <c r="C4595" s="12">
+        <v>1374203</v>
+      </c>
+      <c r="D4595" s="13">
+        <v>30.4</v>
+      </c>
+      <c r="E4595" s="13">
+        <v>26.9</v>
+      </c>
+      <c r="F4595" s="13">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4596" s="2">
         <v>46234</v>
       </c>
-    </row>
-    <row r="4597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4596" s="12">
+        <v>54102888</v>
+      </c>
+      <c r="C4596" s="12">
+        <v>1277930</v>
+      </c>
+      <c r="D4596" s="13">
+        <v>31.3</v>
+      </c>
+      <c r="E4596" s="13">
+        <v>26.1</v>
+      </c>
+      <c r="F4596" s="13">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4597" s="2">
         <v>46235</v>
       </c>
-    </row>
-    <row r="4598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4597" s="12">
+        <v>41518224</v>
+      </c>
+      <c r="C4597" s="12">
+        <v>979600</v>
+      </c>
+      <c r="D4597" s="13">
+        <v>32.5</v>
+      </c>
+      <c r="E4597" s="13">
+        <v>27.7</v>
+      </c>
+      <c r="F4597" s="13">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4598" s="2">
         <v>46236</v>
       </c>
-    </row>
-    <row r="4599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4598" s="12">
+        <v>37143651</v>
+      </c>
+      <c r="C4598" s="12">
+        <v>875121</v>
+      </c>
+      <c r="D4598" s="13">
+        <v>32.9</v>
+      </c>
+      <c r="E4598" s="13">
+        <v>28.8</v>
+      </c>
+      <c r="F4598" s="13">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4599" s="2">
         <v>46237</v>
       </c>
-    </row>
-    <row r="4600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4599" s="12">
+        <v>46450387</v>
+      </c>
+      <c r="C4599" s="12">
+        <v>1091895</v>
+      </c>
+      <c r="D4599" s="13">
+        <v>31.9</v>
+      </c>
+      <c r="E4599" s="13">
+        <v>26.6</v>
+      </c>
+      <c r="F4599" s="13">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4600" s="2">
         <v>46238</v>
       </c>
-    </row>
-    <row r="4601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4600" s="12">
+        <v>49426694</v>
+      </c>
+      <c r="C4600" s="12">
+        <v>1162039</v>
+      </c>
+      <c r="D4600" s="13">
+        <v>30</v>
+      </c>
+      <c r="E4600" s="13">
+        <v>27.4</v>
+      </c>
+      <c r="F4600" s="13">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4601" s="2">
         <v>46239</v>
       </c>
-    </row>
-    <row r="4602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4601" s="12">
+        <v>52790755</v>
+      </c>
+      <c r="C4601" s="12">
+        <v>1243357</v>
+      </c>
+      <c r="D4601" s="13">
+        <v>29.8</v>
+      </c>
+      <c r="E4601" s="13">
+        <v>26.2</v>
+      </c>
+      <c r="F4601" s="13">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4602" s="2">
         <v>46240</v>
       </c>
-    </row>
-    <row r="4603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4602" s="12">
+        <v>59040972</v>
+      </c>
+      <c r="C4602" s="12">
+        <v>1390067</v>
+      </c>
+      <c r="D4602" s="13">
+        <v>29.7</v>
+      </c>
+      <c r="E4602" s="13">
+        <v>25</v>
+      </c>
+      <c r="F4602" s="13">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4603" s="2">
         <v>46241</v>
       </c>
-    </row>
-    <row r="4604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4603" s="12">
+        <v>60144095</v>
+      </c>
+      <c r="C4603" s="12">
+        <v>1417201</v>
+      </c>
+      <c r="D4603" s="13">
+        <v>30.6</v>
+      </c>
+      <c r="E4603" s="13">
+        <v>24.9</v>
+      </c>
+      <c r="F4603" s="13">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="2">
         <v>46242</v>
       </c>
-    </row>
-    <row r="4605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4604" s="12">
+        <v>47355362</v>
+      </c>
+      <c r="C4604" s="12">
+        <v>1115533</v>
+      </c>
+      <c r="D4604" s="13">
+        <v>28.6</v>
+      </c>
+      <c r="E4604" s="13">
+        <v>26.6</v>
+      </c>
+      <c r="F4604" s="13">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="2">
         <v>46243</v>
       </c>
-    </row>
-    <row r="4606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4605" s="12">
+        <v>41871050</v>
+      </c>
+      <c r="C4605" s="12">
+        <v>985854</v>
+      </c>
+      <c r="D4605" s="13">
+        <v>27.5</v>
+      </c>
+      <c r="E4605" s="13">
+        <v>25.6</v>
+      </c>
+      <c r="F4605" s="13">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4606" s="2">
         <v>46244</v>
       </c>
-    </row>
-    <row r="4607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4606" s="12">
+        <v>59992479</v>
+      </c>
+      <c r="C4606" s="12">
+        <v>1411180</v>
+      </c>
+      <c r="D4606" s="13">
+        <v>26.1</v>
+      </c>
+      <c r="E4606" s="13">
+        <v>23.3</v>
+      </c>
+      <c r="F4606" s="13">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4607" s="2">
         <v>46245</v>
       </c>
-    </row>
-    <row r="4608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4607" s="12">
+        <v>63860434</v>
+      </c>
+      <c r="C4607" s="12">
+        <v>1501318</v>
+      </c>
+      <c r="D4607" s="13">
+        <v>24.8</v>
+      </c>
+      <c r="E4607" s="13">
+        <v>21.7</v>
+      </c>
+      <c r="F4607" s="13">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4608" s="2">
         <v>46246</v>
       </c>
-    </row>
-    <row r="4609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4608" s="12">
+        <v>63513716</v>
+      </c>
+      <c r="C4608" s="12">
+        <v>1490843</v>
+      </c>
+      <c r="D4608" s="13">
+        <v>24.7</v>
+      </c>
+      <c r="E4608" s="13">
+        <v>18.8</v>
+      </c>
+      <c r="F4608" s="13">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4609" s="2">
         <v>46247</v>
       </c>
-    </row>
-    <row r="4610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4609" s="12">
+        <v>64663072</v>
+      </c>
+      <c r="C4609" s="12">
+        <v>1518126</v>
+      </c>
+      <c r="D4609" s="13">
+        <v>27.3</v>
+      </c>
+      <c r="E4609" s="13">
+        <v>22.3</v>
+      </c>
+      <c r="F4609" s="13">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4610" s="2">
         <v>46248</v>
       </c>
-    </row>
-    <row r="4611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4610" s="12">
+        <v>63138704</v>
+      </c>
+      <c r="C4610" s="12">
+        <v>1482021</v>
+      </c>
+      <c r="D4610" s="13">
+        <v>28.9</v>
+      </c>
+      <c r="E4610" s="13">
+        <v>23.3</v>
+      </c>
+      <c r="F4610" s="13">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4611" s="2">
         <v>46249</v>
       </c>
-    </row>
-    <row r="4612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4611" s="12">
+        <v>46613306</v>
+      </c>
+      <c r="C4611" s="12">
+        <v>1093671</v>
+      </c>
+      <c r="D4611" s="13">
+        <v>27.7</v>
+      </c>
+      <c r="E4611" s="13">
+        <v>24.3</v>
+      </c>
+      <c r="F4611" s="13">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4612" s="2">
         <v>46250</v>
       </c>
-    </row>
-    <row r="4613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4612" s="12">
+        <v>41786453</v>
+      </c>
+      <c r="C4612" s="12">
+        <v>981404</v>
+      </c>
+      <c r="D4612" s="13">
+        <v>22.7</v>
+      </c>
+      <c r="E4612" s="13">
+        <v>21.4</v>
+      </c>
+      <c r="F4612" s="13">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4613" s="2">
         <v>46251</v>
       </c>
-    </row>
-    <row r="4614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4613" s="12">
+        <v>48513006</v>
+      </c>
+      <c r="C4613" s="12">
+        <v>1139036</v>
+      </c>
+      <c r="D4613" s="13">
+        <v>24.6</v>
+      </c>
+      <c r="E4613" s="13">
+        <v>21.8</v>
+      </c>
+      <c r="F4613" s="13">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4614" s="2">
         <v>46252</v>
       </c>
     </row>
-    <row r="4615" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4615" s="2">
         <v>46253</v>
       </c>
     </row>
-    <row r="4616" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4616" s="2">
         <v>46254</v>
       </c>
     </row>
-    <row r="4617" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4617" s="2">
         <v>46255</v>
       </c>
     </row>
-    <row r="4618" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4618" s="2">
         <v>46256</v>
       </c>
     </row>
-    <row r="4619" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4619" s="2">
         <v>46257</v>
       </c>
     </row>
-    <row r="4620" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4620" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="4621" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4621" s="2">
         <v>46259</v>
       </c>
     </row>
-    <row r="4622" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4622" s="2">
         <v>46260</v>
       </c>
     </row>
-    <row r="4623" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4623" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="4624" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4624" s="2">
         <v>46262</v>
       </c>

--- a/일일공급량_raw.xlsx
+++ b/일일공급량_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\MM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73969A1B-6B2B-4926-B8E0-E9D0F7C3C34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B8C70E-7017-47EB-A58F-2201C79D2031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA341F54-7076-456B-B2A5-63C21B48371E}"/>
   </bookViews>
@@ -420,7 +420,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -581,6 +581,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -710,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +818,18 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -93398,133 +93458,217 @@
       <c r="A4614" s="2">
         <v>46252</v>
       </c>
+      <c r="E4614" s="20">
+        <v>25</v>
+      </c>
+      <c r="F4614" s="22">
+        <v>33</v>
+      </c>
     </row>
     <row r="4615" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4615" s="2">
         <v>46253</v>
       </c>
+      <c r="E4615" s="20">
+        <v>25</v>
+      </c>
+      <c r="F4615" s="22">
+        <v>31</v>
+      </c>
     </row>
     <row r="4616" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4616" s="2">
         <v>46254</v>
       </c>
+      <c r="E4616" s="20">
+        <v>25</v>
+      </c>
+      <c r="F4616" s="22">
+        <v>32</v>
+      </c>
     </row>
     <row r="4617" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4617" s="2">
         <v>46255</v>
       </c>
+      <c r="E4617" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4617" s="22">
+        <v>28</v>
+      </c>
     </row>
     <row r="4618" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4618" s="2">
         <v>46256</v>
       </c>
+      <c r="E4618" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4618" s="22">
+        <v>29</v>
+      </c>
     </row>
     <row r="4619" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4619" s="2">
         <v>46257</v>
       </c>
+      <c r="E4619" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4619" s="22">
+        <v>29</v>
+      </c>
     </row>
     <row r="4620" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4620" s="2">
         <v>46258</v>
       </c>
+      <c r="E4620" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4620" s="22">
+        <v>31</v>
+      </c>
     </row>
     <row r="4621" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4621" s="2">
         <v>46259</v>
       </c>
+      <c r="E4621" s="20">
+        <v>25</v>
+      </c>
+      <c r="F4621" s="22">
+        <v>33</v>
+      </c>
     </row>
     <row r="4622" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4622" s="2">
         <v>46260</v>
       </c>
+      <c r="E4622" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4622" s="22">
+        <v>33</v>
+      </c>
     </row>
     <row r="4623" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4623" s="2">
         <v>46261</v>
       </c>
+      <c r="E4623" s="20">
+        <v>25</v>
+      </c>
+      <c r="F4623" s="22">
+        <v>33</v>
+      </c>
     </row>
     <row r="4624" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4624" s="2">
         <v>46262</v>
       </c>
-    </row>
-    <row r="4625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4624" s="20">
+        <v>24</v>
+      </c>
+      <c r="F4624" s="22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4625" s="2">
         <v>46263</v>
       </c>
-    </row>
-    <row r="4626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4625" s="20">
+        <v>23</v>
+      </c>
+      <c r="F4625" s="22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4626" s="2">
         <v>46264</v>
       </c>
-    </row>
-    <row r="4627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4626" s="20">
+        <v>22</v>
+      </c>
+      <c r="F4626" s="22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4627" s="2">
         <v>46265</v>
       </c>
-    </row>
-    <row r="4628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="E4627" s="21">
+        <v>22</v>
+      </c>
+      <c r="F4627" s="23">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4628" s="2">
         <v>46266</v>
       </c>
     </row>
-    <row r="4629" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4629" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4629" s="2">
         <v>46267</v>
       </c>
     </row>
-    <row r="4630" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4630" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4630" s="2">
         <v>46268</v>
       </c>
     </row>
-    <row r="4631" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4631" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4631" s="2">
         <v>46269</v>
       </c>
     </row>
-    <row r="4632" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4632" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4632" s="2">
         <v>46270</v>
       </c>
     </row>
-    <row r="4633" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4633" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4633" s="2">
         <v>46271</v>
       </c>
     </row>
-    <row r="4634" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4634" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4634" s="2">
         <v>46272</v>
       </c>
     </row>
-    <row r="4635" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4635" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4635" s="2">
         <v>46273</v>
       </c>
     </row>
-    <row r="4636" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4636" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4636" s="2">
         <v>46274</v>
       </c>
     </row>
-    <row r="4637" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4637" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4637" s="2">
         <v>46275</v>
       </c>
     </row>
-    <row r="4638" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4638" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4638" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="4639" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4639" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4639" s="2">
         <v>46277</v>
       </c>
     </row>
-    <row r="4640" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4640" s="2">
         <v>46278</v>
       </c>
